--- a/data/personalia/4 SM.xlsx
+++ b/data/personalia/4 SM.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\OneDrive\Desktop\p3ste-app\Fix\Personalia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\18. STE APP\Personalia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210E0966-85EC-4AA5-892B-5FB09D7F384E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60BF134-C085-4E41-9DFE-4D25710E2BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,10 +17,19 @@
     <sheet name="LIST_DATA" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Template Personalia'!$A$1:$T$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Template Personalia'!$A$1:$T$199</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -29,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="375">
   <si>
     <t>Wilayah</t>
   </si>
@@ -163,12 +172,117 @@
     <t>Kaur UPT Workshop</t>
   </si>
   <si>
+    <t>WS LAA Mri</t>
+  </si>
+  <si>
+    <t>LAA 1.4 Thb</t>
+  </si>
+  <si>
+    <t>Teknisi</t>
+  </si>
+  <si>
+    <t>LAA 1.1 Rk</t>
+  </si>
+  <si>
+    <t>LAA 1.14 Nmo</t>
+  </si>
+  <si>
+    <t>LAA 1.2 Prp</t>
+  </si>
+  <si>
+    <t>LAA 1.3 Srp</t>
+  </si>
+  <si>
+    <t>LAA 1.5 Du</t>
+  </si>
+  <si>
+    <t>LAA 1.11 Psm</t>
+  </si>
+  <si>
+    <t>LAA 1.6 Jakk</t>
+  </si>
+  <si>
+    <t>LAA 1.7 Pse</t>
+  </si>
+  <si>
+    <t>LAA 1.8 Mri</t>
+  </si>
+  <si>
+    <t>LAA 1.9 Jng</t>
+  </si>
+  <si>
+    <t>LAA 1.10 Ckr</t>
+  </si>
+  <si>
+    <t>LAA 1.12 Dp</t>
+  </si>
+  <si>
+    <t>LAA 1.13 Boo</t>
+  </si>
+  <si>
+    <t>LAA 1.15 Bst</t>
+  </si>
+  <si>
+    <t>PMP Lanjutan</t>
+  </si>
+  <si>
+    <t>PMP Pelaksana</t>
+  </si>
+  <si>
+    <t>PRP Pelaksana</t>
+  </si>
+  <si>
+    <t>PRP Lanjutan</t>
+  </si>
+  <si>
+    <t>Calon Pekerja</t>
+  </si>
+  <si>
+    <t>Calon Pelaksana</t>
+  </si>
+  <si>
+    <t>Calon Teknisi</t>
+  </si>
+  <si>
+    <t>Calon Pelaksana Workshop</t>
+  </si>
+  <si>
+    <t>Calon Petugas Negative Check</t>
+  </si>
+  <si>
+    <t>Executive Vice President</t>
+  </si>
+  <si>
+    <t>Kepala UPT BYST</t>
+  </si>
+  <si>
+    <t>Pelaksana Workshop</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Power System 1</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Power System 2</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Signalling And Communication 1</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Signalling And Communication 2</t>
+  </si>
+  <si>
+    <t>Subunit of Workshop And OCC Signalling and Communication</t>
+  </si>
+  <si>
+    <t>Subunit of Workshop Power System And OCC Power</t>
+  </si>
+  <si>
+    <t>Vice President</t>
+  </si>
+  <si>
     <t>Pelaksana Informasi dan Evaluasi</t>
   </si>
   <si>
-    <t>Teknisi</t>
-  </si>
-  <si>
     <t>4 SM</t>
   </si>
   <si>
@@ -184,18 +298,27 @@
     <t>QC STL 4A Pk</t>
   </si>
   <si>
+    <t>PMP.180876.71983</t>
+  </si>
+  <si>
     <t>JOKO SULISTIYO</t>
   </si>
   <si>
     <t>QC STL 4B Smt</t>
   </si>
   <si>
+    <t>PMP.161075.127178</t>
+  </si>
+  <si>
     <t>HERU PRAYITNO</t>
   </si>
   <si>
     <t>QC STL 4C Cu</t>
   </si>
   <si>
+    <t>PMP.211272.126804</t>
+  </si>
+  <si>
     <t>ACHMAD CHARIRI</t>
   </si>
   <si>
@@ -214,15 +337,24 @@
     <t>AM Spesifikasi dan Standarisasi Sintelis Sintelis Daop 4 Sm</t>
   </si>
   <si>
+    <t>PMP.271276.122283</t>
+  </si>
+  <si>
     <t>FIKRY NOOR SHOFWAN</t>
   </si>
   <si>
+    <t>PRP.02021991.37991</t>
+  </si>
+  <si>
     <t>TAMADESTYA BAYU NORAHPRADITA</t>
   </si>
   <si>
     <t>Pelaksana Perencanaan dan Pengendalian Sintelis</t>
   </si>
   <si>
+    <t>PRP.161100.72309</t>
+  </si>
+  <si>
     <t>BUDI RIJANTO</t>
   </si>
   <si>
@@ -232,24 +364,39 @@
     <t>WS Sm</t>
   </si>
   <si>
+    <t>PRP.281073.125905</t>
+  </si>
+  <si>
+    <t>PMP.281073.74123</t>
+  </si>
+  <si>
     <t>LION AGUS SETIAWAN</t>
   </si>
   <si>
     <t>Supervisor Rekayasa Perawatan Workshop Sintelis Semarang</t>
   </si>
   <si>
+    <t>PRP.310785.126170</t>
+  </si>
+  <si>
     <t>FAUSTINUS DEDY ARIWIYANTO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan Workshop Sintelis Semarang</t>
   </si>
   <si>
+    <t>PRP.150285.127159</t>
+  </si>
+  <si>
     <t>YANUAR ASTANTO</t>
   </si>
   <si>
     <t>Teknisi Subunit Perbaikan Workshop Sintelis Semarang</t>
   </si>
   <si>
+    <t>PRP.02011993.37013</t>
+  </si>
+  <si>
     <t>SUTIYONO</t>
   </si>
   <si>
@@ -259,39 +406,66 @@
     <t>4.1 Tg</t>
   </si>
   <si>
+    <t>PRP.100574.126509</t>
+  </si>
+  <si>
+    <t>PMP.100574.71210</t>
+  </si>
+  <si>
     <t>EKO RAHMAT KURNIAWAN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas B 4.1 Tegal</t>
   </si>
   <si>
+    <t>PRP.141289.126511</t>
+  </si>
+  <si>
     <t>ANDRI SETIAWAN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas B 4.1 Tg</t>
   </si>
   <si>
+    <t>PRP.180885.128249</t>
+  </si>
+  <si>
     <t>DIKI SAPUTRO</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 4.1 Tg</t>
   </si>
   <si>
+    <t>PRP.290597.41060</t>
+  </si>
+  <si>
     <t>RHEZA PRANATA TRESNA</t>
   </si>
   <si>
+    <t>PRP.240593.00351</t>
+  </si>
+  <si>
     <t>RUBEN JUNIOR SORA BARROS SOARES</t>
   </si>
   <si>
+    <t>PRP.230100.74131</t>
+  </si>
+  <si>
     <t>ERI PAMBUDI</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 4.1 Tg</t>
   </si>
   <si>
+    <t>PRP.27051995.37341</t>
+  </si>
+  <si>
     <t>ILHAM MAOLANA</t>
   </si>
   <si>
+    <t>PRP.030792.00380</t>
+  </si>
+  <si>
     <t>SUGIARSO</t>
   </si>
   <si>
@@ -301,42 +475,72 @@
     <t>4.2 Pk</t>
   </si>
   <si>
+    <t>PRP. 171073. 126517</t>
+  </si>
+  <si>
+    <t>PMP.171073.74224</t>
+  </si>
+  <si>
     <t>WIDHI ARIANTO SAMBODO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas B 4.2 Pk</t>
   </si>
   <si>
+    <t>PRP.120684.126164</t>
+  </si>
+  <si>
     <t>ZAENAL ARIFIN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas B 4.2 Pk</t>
   </si>
   <si>
+    <t>PRP.230788.00281</t>
+  </si>
+  <si>
     <t>ALIFIO RICKY BIRAYA</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 4.2 Pk</t>
   </si>
   <si>
+    <t>PRP.06111995.37992</t>
+  </si>
+  <si>
     <t>EKO SUPRIYANTO</t>
   </si>
   <si>
+    <t>PRP.04081987.37348</t>
+  </si>
+  <si>
     <t>WAHYU SETYO NUGROHO</t>
   </si>
   <si>
+    <t>PRP.080279.00317</t>
+  </si>
+  <si>
     <t>DIDI RISNANTO</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 4.2 Pk</t>
   </si>
   <si>
+    <t>PRP.230793.117820</t>
+  </si>
+  <si>
     <t>IWAN HENDRA PERMANA</t>
   </si>
   <si>
+    <t>PRP.211093.38624</t>
+  </si>
+  <si>
     <t>MAHRUS ALI</t>
   </si>
   <si>
+    <t>PRP.060198.117827</t>
+  </si>
+  <si>
     <t>BENI SUSANTO</t>
   </si>
   <si>
@@ -346,18 +550,27 @@
     <t>4.3 Btg</t>
   </si>
   <si>
+    <t>PRP.300977.126515</t>
+  </si>
+  <si>
     <t>JOKO BUDIYONO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 4.3 Btg</t>
   </si>
   <si>
+    <t>PRP.150886.00255</t>
+  </si>
+  <si>
     <t>PANJI PRAKARSA</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 4.3 Btg</t>
   </si>
   <si>
+    <t>PRP.130989.00347</t>
+  </si>
+  <si>
     <t>MUCH RIZKI RAMADHAN</t>
   </si>
   <si>
@@ -367,18 +580,30 @@
     <t>M. RIZA KINANTA</t>
   </si>
   <si>
+    <t>PRP.20111992.37015</t>
+  </si>
+  <si>
     <t>MUHAMAD BAGUS CHAIRUL</t>
   </si>
   <si>
+    <t>PRP.140800.68025</t>
+  </si>
+  <si>
     <t>RYANDITYA PRIMADA SYAHPUTRA</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 4.3 Btg</t>
   </si>
   <si>
+    <t>PRP.21031990.37342</t>
+  </si>
+  <si>
     <t>RAHMADAN ALIF HIDAYAH</t>
   </si>
   <si>
+    <t>PRP.221299.73673</t>
+  </si>
+  <si>
     <t>ANDY WIJAYA</t>
   </si>
   <si>
@@ -388,39 +613,66 @@
     <t>4.4 Wlr</t>
   </si>
   <si>
+    <t>PRP.230878.127714</t>
+  </si>
+  <si>
+    <t>PMP.230878.67646</t>
+  </si>
+  <si>
     <t>HERMAN SIDIK</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 4.4 Wlr</t>
   </si>
   <si>
+    <t>PRP.190788.00316</t>
+  </si>
+  <si>
     <t>AJI SEMBODO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 4.4 Wlr</t>
   </si>
   <si>
+    <t>PRP.270483.126733</t>
+  </si>
+  <si>
     <t>HERI BUDIYANTO</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 4.4 Wlr</t>
   </si>
   <si>
+    <t>PRP.021281.00341</t>
+  </si>
+  <si>
     <t>APRI SUPRIYANTONO</t>
   </si>
   <si>
+    <t>PRP.010487.00338</t>
+  </si>
+  <si>
     <t>HAPPINUS WIMARTANTO</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 4.4 Wlr</t>
   </si>
   <si>
+    <t>PRP.130376.00315</t>
+  </si>
+  <si>
     <t>MUHAMAD ABDULLATIF</t>
   </si>
   <si>
+    <t>PRP.310396.41061</t>
+  </si>
+  <si>
     <t>RAMADHAN WIDYA PUTRA</t>
   </si>
   <si>
+    <t>PRP.21021995.37350</t>
+  </si>
+  <si>
     <t>MUHAMMAD NURYONO</t>
   </si>
   <si>
@@ -430,39 +682,66 @@
     <t>4.5 Kln</t>
   </si>
   <si>
+    <t>PRP.240873.126165</t>
+  </si>
+  <si>
+    <t>PMP.240873.74124</t>
+  </si>
+  <si>
     <t>AGUS PRASETYO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 4.5 Kln</t>
   </si>
   <si>
+    <t>PRP.070890.00278</t>
+  </si>
+  <si>
     <t>LAKSONO CIPTO PAMUNGKAS</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 4.5 Kln</t>
   </si>
   <si>
+    <t>PRP.180689.127713</t>
+  </si>
+  <si>
     <t>AGUNG PRADANA</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 4.5 Kln</t>
   </si>
   <si>
+    <t>PRP.190490.00235</t>
+  </si>
+  <si>
     <t>BENY PORWANTO</t>
   </si>
   <si>
+    <t>PRP.101292.41059</t>
+  </si>
+  <si>
     <t>KHOERUL UMAM</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 4.5 Kln</t>
   </si>
   <si>
+    <t>PRP.020196.117824</t>
+  </si>
+  <si>
     <t>M. ZILZAL ROZIQIN</t>
   </si>
   <si>
+    <t>PRP.140993.117826</t>
+  </si>
+  <si>
     <t>JATU AGUNG SEMBADA</t>
   </si>
   <si>
+    <t>PRP.150494.117823</t>
+  </si>
+  <si>
     <t>APRIYADI</t>
   </si>
   <si>
@@ -472,45 +751,78 @@
     <t>4.6 Smt</t>
   </si>
   <si>
+    <t>PRP.051076.126270</t>
+  </si>
+  <si>
+    <t>PMP.051076.69659</t>
+  </si>
+  <si>
     <t>SETIYONO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas B 4.6 Smt</t>
   </si>
   <si>
+    <t>PRP.080489.128248</t>
+  </si>
+  <si>
     <t>ADITYA ROCHMAN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas B 4.6 Smt</t>
   </si>
   <si>
+    <t>PRP.151282.126548</t>
+  </si>
+  <si>
     <t>IBNU CANDRA</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 4.6 Smt</t>
   </si>
   <si>
+    <t>PRP.220491.00254</t>
+  </si>
+  <si>
     <t>BAGAS MAHENDRA PUTRA</t>
   </si>
   <si>
+    <t>PRP.310792.00282</t>
+  </si>
+  <si>
     <t>YUSRIFAR IMAM HARITSAH</t>
   </si>
   <si>
+    <t>PRP.091096.39437</t>
+  </si>
+  <si>
     <t>ZURKHAN FAHRUDIN</t>
   </si>
   <si>
+    <t>PRP.040492.00318</t>
+  </si>
+  <si>
     <t>ABDUL ROHMAN</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 4.6 Smt</t>
   </si>
   <si>
+    <t>PRP.040383.00277</t>
+  </si>
+  <si>
     <t>DEDE ROMADONI</t>
   </si>
   <si>
+    <t>PRP.090392.00312</t>
+  </si>
+  <si>
     <t>DHANI ADITYA WIDARMADI</t>
   </si>
   <si>
+    <t>PRP.17071997.37345</t>
+  </si>
+  <si>
     <t>ARIF SURYANTO</t>
   </si>
   <si>
@@ -526,36 +838,60 @@
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 4.7 Gd</t>
   </si>
   <si>
+    <t>PRP.220582.00349</t>
+  </si>
+  <si>
     <t>AHMAD SUPRIYANTO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 4.7 Gd</t>
   </si>
   <si>
+    <t>PRP.280284.00249</t>
+  </si>
+  <si>
     <t>AGUNG UTOMO</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 4.7 Gd</t>
   </si>
   <si>
+    <t>PRP.17011989.37347</t>
+  </si>
+  <si>
     <t>GALIH ANJAR KURNIAWAN</t>
   </si>
   <si>
+    <t>PRP.010392.00605</t>
+  </si>
+  <si>
     <t>DWI PUJA AFRIALDI</t>
   </si>
   <si>
+    <t>PRP.300498.117821</t>
+  </si>
+  <si>
     <t>MUCHLISIN</t>
   </si>
   <si>
+    <t>PRP.230682.00345</t>
+  </si>
+  <si>
     <t>ILHAM ZAKARIYA</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 4.7 Gd</t>
   </si>
   <si>
+    <t>PRP.170303.56554</t>
+  </si>
+  <si>
     <t>SIFNI MAVAZATUL HAYAT</t>
   </si>
   <si>
+    <t>PRP.051202.72842</t>
+  </si>
+  <si>
     <t>ANANTA HENDRA PRASETYA</t>
   </si>
   <si>
@@ -565,42 +901,72 @@
     <t>4.8 Bbg</t>
   </si>
   <si>
+    <t>PRP.161286.126510</t>
+  </si>
+  <si>
+    <t>PMP.161286.67704</t>
+  </si>
+  <si>
     <t>RONI LUKMAN HIDAYAT</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 4.8 Bbg</t>
   </si>
   <si>
+    <t>PRP.290782.127303</t>
+  </si>
+  <si>
     <t>TEGUH TYAS PRASETYO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 4.8 Bbg</t>
   </si>
   <si>
+    <t>PRP.040988.00348</t>
+  </si>
+  <si>
     <t>SYAUQI NUR AZIZ</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 4.8 Bbg</t>
   </si>
   <si>
+    <t>PRP.300900.74229</t>
+  </si>
+  <si>
     <t>FAJAR BUDI SAMUDRA</t>
   </si>
   <si>
+    <t>PRP.04051994.37346</t>
+  </si>
+  <si>
     <t>MUHAMMAD BAGUS SAEPUTRA</t>
   </si>
   <si>
+    <t>PRP.170685.00346</t>
+  </si>
+  <si>
     <t>M. SABILI MUTAQIN</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 4.8 Bbg</t>
   </si>
   <si>
+    <t>PRP.25051992.37344</t>
+  </si>
+  <si>
     <t>ILHAM FRENDI PRAKOSO</t>
   </si>
   <si>
+    <t>PRP.160503.67708</t>
+  </si>
+  <si>
     <t>DIMAST BAGAS PERMANA</t>
   </si>
   <si>
+    <t>PRP.140701.71433</t>
+  </si>
+  <si>
     <t>AGUNG SUGIHARTANTO</t>
   </si>
   <si>
@@ -610,39 +976,66 @@
     <t>4.9 Gbn</t>
   </si>
   <si>
+    <t>PRP.140976.125898</t>
+  </si>
+  <si>
+    <t>PMP.140976.69661</t>
+  </si>
+  <si>
     <t>MUCHAMAD NORWIYANTO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 4.9 Gbn</t>
   </si>
   <si>
+    <t>PRP.240886.126516</t>
+  </si>
+  <si>
     <t>MUHAMAD RULY HIDAYAT</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 4.9 Gbn</t>
   </si>
   <si>
+    <t>PRP.180689.00350</t>
+  </si>
+  <si>
     <t>JUMADI</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 4.9 Gbn</t>
   </si>
   <si>
+    <t>PRP.100878.00342</t>
+  </si>
+  <si>
     <t>DESTAVERNANDA</t>
   </si>
   <si>
+    <t>PRP.191296.117819</t>
+  </si>
+  <si>
     <t>MUHAMMAD MULTAZAM</t>
   </si>
   <si>
+    <t>PRP.090798.72840</t>
+  </si>
+  <si>
     <t>PATRIA AHMAD HAMDANI</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 4.9 Gbn</t>
   </si>
   <si>
+    <t>PRP.301292.117829</t>
+  </si>
+  <si>
     <t>SAIFUL APRIYANTO</t>
   </si>
   <si>
+    <t>PRP.090498.72841</t>
+  </si>
+  <si>
     <t>MULYADI</t>
   </si>
   <si>
@@ -652,36 +1045,60 @@
     <t>4.10 Knn</t>
   </si>
   <si>
+    <t>PRP.040675.127302</t>
+  </si>
+  <si>
+    <t>PMP.040675.75599</t>
+  </si>
+  <si>
     <t>EDY TRI PRAYITNO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 4.10 Knn</t>
   </si>
   <si>
+    <t>PRP.260493.00314</t>
+  </si>
+  <si>
     <t>TRI APRILLIONO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 4.10 Knn</t>
   </si>
   <si>
+    <t>PRP.080487.00592</t>
+  </si>
+  <si>
     <t>MUCHAMAD YUSUP ANDRIANSYAH</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 4.10 Knn</t>
   </si>
   <si>
+    <t>PRP.101001.65327</t>
+  </si>
+  <si>
     <t>SANJAYA</t>
   </si>
   <si>
+    <t>PRP.260894.02323</t>
+  </si>
+  <si>
     <t>ERICK ADI SURYA</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 4.10 Knn</t>
   </si>
   <si>
+    <t>PRP.240195.121143</t>
+  </si>
+  <si>
     <t>ALMAKH FUNDON</t>
   </si>
   <si>
+    <t>PRP.23051982.38430</t>
+  </si>
+  <si>
     <t>AGUNG PRI PRABOWO</t>
   </si>
   <si>
@@ -691,316 +1108,61 @@
     <t>4.11 Cu</t>
   </si>
   <si>
+    <t>PRP.11011989.38431</t>
+  </si>
+  <si>
     <t>MUHHAMMAD ALI WENNAZ</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 4.11 Cu</t>
   </si>
   <si>
+    <t>PRP.301085.00383</t>
+  </si>
+  <si>
     <t>ANDI PUTRA KURNIAWAN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 4.11 Cu</t>
   </si>
   <si>
+    <t>PRP.210891.00250</t>
+  </si>
+  <si>
     <t>AHMAD CHOIRUL ANWAR</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 4.11 Cu</t>
   </si>
   <si>
+    <t>PRP.090794.00309</t>
+  </si>
+  <si>
     <t>ILHAM HABIB BAHARUDIN</t>
   </si>
   <si>
+    <t>PRP.160502.72054</t>
+  </si>
+  <si>
     <t>MOCHAMAD ASEP</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 4.11 Cu</t>
   </si>
   <si>
+    <t>PRP.161095.117828</t>
+  </si>
+  <si>
     <t>RISKI EDHO PERMANA</t>
   </si>
   <si>
+    <t>PRP.28121997.37343</t>
+  </si>
+  <si>
     <t>ADHITYA WAHANA PUTRA</t>
   </si>
   <si>
-    <t>PRP. 180876. 126737</t>
-  </si>
-  <si>
-    <t>PMP.161075.127178</t>
-  </si>
-  <si>
-    <t>PMP. 211272. 126804</t>
-  </si>
-  <si>
-    <t>PRP. 271275. 126984</t>
-  </si>
-  <si>
-    <t>PMP.22091989.29359</t>
-  </si>
-  <si>
-    <t>PMP.271276.122283</t>
-  </si>
-  <si>
-    <t>PRP.02021991.37991</t>
-  </si>
-  <si>
-    <t>PRP.161100.72309</t>
-  </si>
-  <si>
-    <t>PRP.281073.125905</t>
-  </si>
-  <si>
-    <t>PRP.150285.127159</t>
-  </si>
-  <si>
-    <t>PRP.02011993.37013</t>
-  </si>
-  <si>
-    <t>PRP.100574.126509</t>
-  </si>
-  <si>
-    <t>PRP.141289.126511</t>
-  </si>
-  <si>
-    <t>PRP.180885.128249</t>
-  </si>
-  <si>
-    <t>PRP.290597.41060</t>
-  </si>
-  <si>
-    <t>PRP.240593.00351</t>
-  </si>
-  <si>
-    <t>PRP.230100.74131</t>
-  </si>
-  <si>
-    <t>PRP.27051995.37341</t>
-  </si>
-  <si>
-    <t>PRP.030792.00380</t>
-  </si>
-  <si>
-    <t>PRP. 171073. 126517</t>
-  </si>
-  <si>
-    <t>PRP.230788.00281</t>
-  </si>
-  <si>
-    <t>PRP.04081987.37348</t>
-  </si>
-  <si>
-    <t>PRP.080279.00317</t>
-  </si>
-  <si>
-    <t>PRP.230793.117820</t>
-  </si>
-  <si>
-    <t>PRP.211093.38624</t>
-  </si>
-  <si>
-    <t>PRP.060198.117827</t>
-  </si>
-  <si>
-    <t>PRP.150886.00255</t>
-  </si>
-  <si>
-    <t>PRP.130989.00347</t>
-  </si>
-  <si>
-    <t>PRP.140800.68025</t>
-  </si>
-  <si>
-    <t>PRP.21031990.37342</t>
-  </si>
-  <si>
-    <t>PRP.221299.73673</t>
-  </si>
-  <si>
-    <t>PRP.230878.127714</t>
-  </si>
-  <si>
-    <t>PRP.270483.126733</t>
-  </si>
-  <si>
-    <t>PRP.021281.00341</t>
-  </si>
-  <si>
-    <t>PRP.010487.00338</t>
-  </si>
-  <si>
-    <t>PRP.21021995.37350</t>
-  </si>
-  <si>
-    <t>PRP.240873.126165</t>
-  </si>
-  <si>
-    <t>PRP.180689.127713</t>
-  </si>
-  <si>
-    <t>PRP.190490.00235</t>
-  </si>
-  <si>
-    <t>PRP.020196.117824</t>
-  </si>
-  <si>
-    <t>PRP.140993.117826</t>
-  </si>
-  <si>
-    <t>PRP.150494.117823</t>
-  </si>
-  <si>
-    <t>PRP.051076.126270</t>
-  </si>
-  <si>
-    <t>PRP.151282.126548</t>
-  </si>
-  <si>
-    <t>PRP.220491.00254</t>
-  </si>
-  <si>
-    <t>PRP.310792.00282</t>
-  </si>
-  <si>
-    <t>PRP.091096.39437</t>
-  </si>
-  <si>
-    <t>PRP.040492.00318</t>
-  </si>
-  <si>
-    <t>PRP.040383.00277</t>
-  </si>
-  <si>
-    <t>PRP.090392.00312</t>
-  </si>
-  <si>
-    <t>PRP.17071997.37345</t>
-  </si>
-  <si>
-    <t>PRP 16081988 29515</t>
-  </si>
-  <si>
-    <t>PRP.220582.00349</t>
-  </si>
-  <si>
-    <t>PRP.280284.00249</t>
-  </si>
-  <si>
-    <t>PRP.17011989.37347</t>
-  </si>
-  <si>
-    <t>PRP.300498.117821</t>
-  </si>
-  <si>
-    <t>PRP.170303.56554</t>
-  </si>
-  <si>
-    <t>PRP.051202.72842</t>
-  </si>
-  <si>
-    <t>PRP.161286.126510</t>
-  </si>
-  <si>
-    <t>PRP.040988.00348</t>
-  </si>
-  <si>
-    <t>PRP.300900.74229</t>
-  </si>
-  <si>
-    <t>PRP.04051994.37346</t>
-  </si>
-  <si>
-    <t>PRP.170685.00346</t>
-  </si>
-  <si>
-    <t>PRP.25051992.37344</t>
-  </si>
-  <si>
-    <t>PRP.160503.67708</t>
-  </si>
-  <si>
-    <t>PRP.140701.71433</t>
-  </si>
-  <si>
-    <t>PRP.180689.00350</t>
-  </si>
-  <si>
-    <t>PRP.100878.00342</t>
-  </si>
-  <si>
-    <t>PRP.191296.117819</t>
-  </si>
-  <si>
-    <t>PRP.090798.72840</t>
-  </si>
-  <si>
-    <t>PRP.301292.117829</t>
-  </si>
-  <si>
-    <t>PRP.090498.72841</t>
-  </si>
-  <si>
-    <t>PRP.080487.00592</t>
-  </si>
-  <si>
-    <t>PRP.260894.02323</t>
-  </si>
-  <si>
-    <t>PRP.240195.121143</t>
-  </si>
-  <si>
-    <t>PRP.23051982.38430</t>
-  </si>
-  <si>
-    <t>PRP.11011989.38431</t>
-  </si>
-  <si>
-    <t>PRP.301085.00383</t>
-  </si>
-  <si>
-    <t>PRP.210891.00250</t>
-  </si>
-  <si>
-    <t>PRP.090794.00309</t>
-  </si>
-  <si>
-    <t>PRP.160502.72054</t>
-  </si>
-  <si>
-    <t>PRP.161095.117828</t>
-  </si>
-  <si>
-    <t>PRP.28121997.37343</t>
-  </si>
-  <si>
     <t>PRP.191297.56553</t>
-  </si>
-  <si>
-    <t>PMP.180876.71983</t>
-  </si>
-  <si>
-    <t>PMP.211272.126804</t>
-  </si>
-  <si>
-    <t>PMP.281073.74123</t>
-  </si>
-  <si>
-    <t>PMP.100574.71210</t>
-  </si>
-  <si>
-    <t>PMP.171073.74224</t>
-  </si>
-  <si>
-    <t>PMP.230878.67646</t>
-  </si>
-  <si>
-    <t>PMP.240873.74124</t>
-  </si>
-  <si>
-    <t>PMP.051076.69659</t>
-  </si>
-  <si>
-    <t>PMP.161286.67704</t>
   </si>
 </sst>
 </file>
@@ -1071,9 +1233,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1082,8 +1241,11 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1387,30 +1549,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T106"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.15" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:T200"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.15" zeroHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.86328125" style="2" customWidth="1"/>
     <col min="2" max="2" width="27.265625" style="3" customWidth="1"/>
     <col min="3" max="3" width="7.86328125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.59765625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.59765625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="32" style="4" customWidth="1"/>
-    <col min="7" max="7" width="8.46484375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.1328125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="20.59765625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21.53125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="32" style="7" customWidth="1"/>
+    <col min="7" max="7" width="12.1328125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.1328125" style="5" customWidth="1"/>
     <col min="9" max="9" width="7.06640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="10.73046875" style="2" customWidth="1"/>
-    <col min="11" max="13" width="13.1328125" style="6" customWidth="1"/>
+    <col min="11" max="13" width="13.1328125" style="5" customWidth="1"/>
     <col min="14" max="14" width="22" style="2" customWidth="1"/>
-    <col min="15" max="15" width="13.1328125" style="6" customWidth="1"/>
+    <col min="15" max="15" width="13.1328125" style="5" customWidth="1"/>
     <col min="16" max="17" width="22" style="2" customWidth="1"/>
-    <col min="18" max="18" width="13.1328125" style="6" customWidth="1"/>
-    <col min="19" max="19" width="22" style="2" customWidth="1"/>
-    <col min="20" max="20" width="22" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.1328125" style="5" customWidth="1"/>
+    <col min="19" max="20" width="22" style="2" customWidth="1"/>
     <col min="21" max="16384" width="9.06640625" style="3" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="5" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:20" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1432,7 +1593,7 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -1441,19 +1602,19 @@
       <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="6" t="s">
         <v>13</v>
       </c>
       <c r="P1" s="1" t="s">
@@ -1462,7 +1623,7 @@
       <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="R1" s="6" t="s">
         <v>16</v>
       </c>
       <c r="S1" s="1" t="s">
@@ -1474,10 +1635,10 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="C2" s="2">
         <v>41150</v>
@@ -1488,13 +1649,13 @@
       <c r="E2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>48</v>
+      <c r="F2" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="5">
         <v>45903</v>
       </c>
       <c r="I2" s="2">
@@ -1503,23 +1664,22 @@
       <c r="J2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="6">
-        <v>45261</v>
-      </c>
-      <c r="L2" s="6">
-        <v>27292</v>
-      </c>
-      <c r="M2" s="6">
-        <v>47757</v>
-      </c>
-      <c r="S2" s="3"/>
+      <c r="K2" s="5">
+        <v>34304</v>
+      </c>
+      <c r="L2" s="5">
+        <v>26721</v>
+      </c>
+      <c r="M2" s="5">
+        <v>47178</v>
+      </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2">
         <v>44529</v>
@@ -1530,14 +1690,14 @@
       <c r="E3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>50</v>
+      <c r="F3" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="6">
-        <v>46060</v>
+      <c r="H3" s="5">
+        <v>45641</v>
       </c>
       <c r="I3" s="2">
         <v>11</v>
@@ -1545,34 +1705,31 @@
       <c r="J3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="6">
-        <v>35070</v>
-      </c>
-      <c r="L3" s="6">
+      <c r="K3" s="5">
+        <v>35217</v>
+      </c>
+      <c r="L3" s="5">
         <v>27990</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="5">
         <v>48458</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="O3" s="6">
-        <v>45696</v>
-      </c>
       <c r="Q3" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="R3" s="6">
+        <v>86</v>
+      </c>
+      <c r="R3" s="5">
         <v>47265</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="C4" s="2">
         <v>46277</v>
@@ -1583,13 +1740,13 @@
       <c r="E4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>52</v>
+      <c r="F4" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>45884</v>
       </c>
       <c r="I4" s="2">
@@ -1598,35 +1755,31 @@
       <c r="J4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>35490</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="5">
         <v>27683</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="5">
         <v>48153</v>
       </c>
-      <c r="N4" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="O4" s="6">
+      <c r="Q4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="R4" s="5">
         <v>46950</v>
       </c>
-      <c r="Q4" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="R4" s="6">
-        <v>46950</v>
-      </c>
-      <c r="S4" s="3"/>
+      <c r="S4" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>53</v>
+        <v>90</v>
       </c>
       <c r="C5" s="2">
         <v>41120</v>
@@ -1637,13 +1790,13 @@
       <c r="E5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>54</v>
+      <c r="F5" s="7" t="s">
+        <v>91</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>45792</v>
       </c>
       <c r="I5" s="2">
@@ -1652,35 +1805,31 @@
       <c r="J5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="5">
         <v>34304</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="5">
         <v>26654</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="5">
         <v>47119</v>
       </c>
-      <c r="N5" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="O5" s="6">
-        <v>45696</v>
-      </c>
       <c r="Q5" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="R5" s="6">
+        <v>92</v>
+      </c>
+      <c r="R5" s="5">
         <v>47265</v>
       </c>
-      <c r="S5" s="3"/>
+      <c r="S5" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="6" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="C6" s="2">
         <v>46279</v>
@@ -1691,13 +1840,13 @@
       <c r="E6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>56</v>
+      <c r="F6" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>45962</v>
       </c>
       <c r="I6" s="2">
@@ -1706,28 +1855,22 @@
       <c r="J6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <v>35490</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="5">
         <v>27755</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="5">
         <v>48214</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="O6" s="6">
-        <v>45696</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2">
         <v>62004</v>
@@ -1738,13 +1881,13 @@
       <c r="E7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>58</v>
+      <c r="F7" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <v>45703</v>
       </c>
       <c r="I7" s="2">
@@ -1753,35 +1896,22 @@
       <c r="J7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="5">
         <v>41153</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="5">
         <v>32773</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="5">
         <v>53236</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="O7" s="6">
-        <v>45810</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="R7" s="6">
-        <v>45810</v>
-      </c>
-      <c r="S7" s="3"/>
     </row>
     <row r="8" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="C8" s="2">
         <v>44530</v>
@@ -1792,13 +1922,13 @@
       <c r="E8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>60</v>
+      <c r="F8" s="7" t="s">
+        <v>98</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <v>45809</v>
       </c>
       <c r="I8" s="2">
@@ -1807,35 +1937,31 @@
       <c r="J8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="5">
         <v>35217</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="5">
         <v>28121</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="5">
         <v>48580</v>
       </c>
-      <c r="N8" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="O8" s="6">
+      <c r="Q8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="R8" s="5">
         <v>46851</v>
       </c>
-      <c r="Q8" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="R8" s="6">
-        <v>46851</v>
-      </c>
-      <c r="S8" s="3"/>
+      <c r="S8" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>61</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2">
         <v>69877</v>
@@ -1846,14 +1972,14 @@
       <c r="E9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>44</v>
+      <c r="F9" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="6">
-        <v>44927</v>
+      <c r="H9" s="5">
+        <v>43191</v>
       </c>
       <c r="I9" s="2">
         <v>4</v>
@@ -1861,29 +1987,31 @@
       <c r="J9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="5">
         <v>42597</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="5">
         <v>33271</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="5">
         <v>53752</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="O9" s="6">
+        <v>101</v>
+      </c>
+      <c r="O9" s="5">
         <v>46305</v>
       </c>
-      <c r="S9" s="3"/>
+      <c r="P9" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="10" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="C10" s="2">
         <v>75324</v>
@@ -1894,13 +2022,13 @@
       <c r="E10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>63</v>
+      <c r="F10" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="5">
         <v>45992</v>
       </c>
       <c r="I10" s="2">
@@ -1909,29 +2037,31 @@
       <c r="J10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="5">
         <v>44958</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="5">
         <v>36846</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="5">
         <v>57315</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="O10" s="6">
+        <v>104</v>
+      </c>
+      <c r="O10" s="5">
         <v>47285</v>
       </c>
-      <c r="S10" s="3"/>
+      <c r="P10" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="C11" s="2">
         <v>43005</v>
@@ -1942,13 +2072,13 @@
       <c r="E11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>65</v>
+      <c r="F11" s="7" t="s">
+        <v>106</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H11" s="6">
+        <v>107</v>
+      </c>
+      <c r="H11" s="5">
         <v>45054</v>
       </c>
       <c r="I11" s="2">
@@ -1957,35 +2087,40 @@
       <c r="J11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="5">
         <v>34790</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="5">
         <v>26965</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="5">
         <v>47423</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="O11" s="6">
+        <v>108</v>
+      </c>
+      <c r="O11" s="5">
         <v>47005</v>
       </c>
+      <c r="P11" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q11" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="R11" s="6">
+        <v>109</v>
+      </c>
+      <c r="R11" s="5">
         <v>47324</v>
       </c>
-      <c r="S11" s="3"/>
+      <c r="S11" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="12" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>67</v>
+        <v>110</v>
       </c>
       <c r="C12" s="2">
         <v>49753</v>
@@ -1996,13 +2131,13 @@
       <c r="E12" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>68</v>
+      <c r="F12" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H12" s="6">
+        <v>107</v>
+      </c>
+      <c r="H12" s="5">
         <v>45731</v>
       </c>
       <c r="I12" s="2">
@@ -2011,23 +2146,31 @@
       <c r="J12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="5">
         <v>39387</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="5">
         <v>31259</v>
       </c>
-      <c r="M12" s="6">
+      <c r="M12" s="5">
         <v>51714</v>
       </c>
-      <c r="S12" s="3"/>
+      <c r="N12" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="O12" s="5">
+        <v>46916</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="13" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="C13" s="2">
         <v>49690</v>
@@ -2038,13 +2181,13 @@
       <c r="E13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>70</v>
+      <c r="F13" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H13" s="6">
+        <v>107</v>
+      </c>
+      <c r="H13" s="5">
         <v>45962</v>
       </c>
       <c r="I13" s="2">
@@ -2053,29 +2196,31 @@
       <c r="J13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="5">
         <v>39387</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="5">
         <v>31093</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M13" s="5">
         <v>51561</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="O13" s="6">
+        <v>115</v>
+      </c>
+      <c r="O13" s="5">
         <v>47114</v>
       </c>
-      <c r="S13" s="3"/>
+      <c r="P13" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="14" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="C14" s="2">
         <v>69861</v>
@@ -2084,16 +2229,16 @@
         <v>33</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>72</v>
+        <v>46</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>117</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H14" s="6">
-        <v>45474</v>
+        <v>107</v>
+      </c>
+      <c r="H14" s="5">
+        <v>45275</v>
       </c>
       <c r="I14" s="2">
         <v>5</v>
@@ -2101,28 +2246,31 @@
       <c r="J14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="5">
         <v>42597</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="5">
         <v>33971</v>
       </c>
-      <c r="M14" s="6">
+      <c r="M14" s="5">
         <v>54455</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="O14" s="6">
+        <v>118</v>
+      </c>
+      <c r="O14" s="5">
         <v>46246</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="C15" s="2">
         <v>45742</v>
@@ -2133,13 +2281,13 @@
       <c r="E15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>74</v>
+      <c r="F15" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H15" s="6">
+        <v>121</v>
+      </c>
+      <c r="H15" s="5">
         <v>45992</v>
       </c>
       <c r="I15" s="2">
@@ -2148,35 +2296,40 @@
       <c r="J15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="5">
         <v>35490</v>
       </c>
-      <c r="L15" s="6">
+      <c r="L15" s="5">
         <v>27159</v>
       </c>
-      <c r="M15" s="6">
+      <c r="M15" s="5">
         <v>47635</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="O15" s="6">
+        <v>122</v>
+      </c>
+      <c r="O15" s="5">
         <v>46998</v>
       </c>
+      <c r="P15" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q15" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="R15" s="6">
+        <v>123</v>
+      </c>
+      <c r="R15" s="5">
         <v>47265</v>
       </c>
-      <c r="S15" s="3"/>
+      <c r="S15" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="16" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="C16" s="2">
         <v>55373</v>
@@ -2187,13 +2340,13 @@
       <c r="E16" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>77</v>
+      <c r="F16" s="7" t="s">
+        <v>125</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H16" s="6">
+        <v>121</v>
+      </c>
+      <c r="H16" s="5">
         <v>45962</v>
       </c>
       <c r="I16" s="2">
@@ -2202,29 +2355,31 @@
       <c r="J16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="5">
         <v>40163</v>
       </c>
-      <c r="L16" s="6">
+      <c r="L16" s="5">
         <v>32856</v>
       </c>
-      <c r="M16" s="6">
+      <c r="M16" s="5">
         <v>53328</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="O16" s="6">
+        <v>126</v>
+      </c>
+      <c r="O16" s="5">
         <v>46973</v>
       </c>
-      <c r="S16" s="3"/>
+      <c r="P16" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="17" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="C17" s="2">
         <v>49762</v>
@@ -2235,13 +2390,13 @@
       <c r="E17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>79</v>
+      <c r="F17" s="7" t="s">
+        <v>128</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H17" s="6">
+        <v>121</v>
+      </c>
+      <c r="H17" s="5">
         <v>45915</v>
       </c>
       <c r="I17" s="2">
@@ -2250,29 +2405,31 @@
       <c r="J17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="5">
         <v>39387</v>
       </c>
-      <c r="L17" s="6">
+      <c r="L17" s="5">
         <v>31277</v>
       </c>
-      <c r="M17" s="6">
+      <c r="M17" s="5">
         <v>51745</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="O17" s="6">
+        <v>129</v>
+      </c>
+      <c r="O17" s="5">
         <v>47114</v>
       </c>
-      <c r="S17" s="3"/>
+      <c r="P17" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="C18" s="2">
         <v>70805</v>
@@ -2283,13 +2440,13 @@
       <c r="E18" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>81</v>
+      <c r="F18" s="7" t="s">
+        <v>131</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H18" s="6">
+        <v>121</v>
+      </c>
+      <c r="H18" s="5">
         <v>45474</v>
       </c>
       <c r="I18" s="2">
@@ -2298,29 +2455,31 @@
       <c r="J18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="5">
         <v>42725</v>
       </c>
-      <c r="L18" s="6">
+      <c r="L18" s="5">
         <v>35579</v>
       </c>
-      <c r="M18" s="6">
+      <c r="M18" s="5">
         <v>56036</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="O18" s="6">
+        <v>132</v>
+      </c>
+      <c r="O18" s="5">
         <v>46448</v>
       </c>
-      <c r="S18" s="3"/>
+      <c r="P18" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="C19" s="2">
         <v>61323</v>
@@ -2331,14 +2490,14 @@
       <c r="E19" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>81</v>
+      <c r="F19" s="7" t="s">
+        <v>131</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H19" s="6">
-        <v>44927</v>
+        <v>121</v>
+      </c>
+      <c r="H19" s="5">
+        <v>44727</v>
       </c>
       <c r="I19" s="2">
         <v>5</v>
@@ -2346,29 +2505,31 @@
       <c r="J19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K19" s="6">
-        <v>40552</v>
-      </c>
-      <c r="L19" s="6">
-        <v>34113</v>
-      </c>
-      <c r="M19" s="6">
+      <c r="K19" s="5">
+        <v>40787</v>
+      </c>
+      <c r="L19" s="5">
+        <v>34112</v>
+      </c>
+      <c r="M19" s="5">
         <v>54575</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="O19" s="6">
+        <v>134</v>
+      </c>
+      <c r="O19" s="5">
         <v>47005</v>
       </c>
-      <c r="S19" s="3"/>
+      <c r="P19" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>83</v>
+        <v>135</v>
       </c>
       <c r="C20" s="2">
         <v>75322</v>
@@ -2379,13 +2540,13 @@
       <c r="E20" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>81</v>
+      <c r="F20" s="7" t="s">
+        <v>131</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H20" s="6">
+        <v>121</v>
+      </c>
+      <c r="H20" s="5">
         <v>45597</v>
       </c>
       <c r="I20" s="2">
@@ -2394,29 +2555,31 @@
       <c r="J20" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K20" s="6">
+      <c r="K20" s="5">
         <v>44958</v>
       </c>
-      <c r="L20" s="6">
+      <c r="L20" s="5">
         <v>36548</v>
       </c>
-      <c r="M20" s="6">
+      <c r="M20" s="5">
         <v>57011</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="O20" s="6">
+        <v>136</v>
+      </c>
+      <c r="O20" s="5">
         <v>47324</v>
       </c>
-      <c r="S20" s="3"/>
+      <c r="P20" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="C21" s="2">
         <v>70293</v>
@@ -2427,13 +2590,13 @@
       <c r="E21" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>85</v>
+      <c r="F21" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H21" s="6">
+        <v>121</v>
+      </c>
+      <c r="H21" s="5">
         <v>45474</v>
       </c>
       <c r="I21" s="2">
@@ -2442,28 +2605,31 @@
       <c r="J21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="5">
         <v>42675</v>
       </c>
-      <c r="L21" s="6">
+      <c r="L21" s="5">
         <v>34846</v>
       </c>
-      <c r="M21" s="6">
+      <c r="M21" s="5">
         <v>55305</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="O21" s="6">
+        <v>139</v>
+      </c>
+      <c r="O21" s="5">
         <v>46259</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>86</v>
+        <v>140</v>
       </c>
       <c r="C22" s="2">
         <v>61307</v>
@@ -2474,13 +2640,13 @@
       <c r="E22" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>85</v>
+      <c r="F22" s="7" t="s">
+        <v>138</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H22" s="6">
+        <v>121</v>
+      </c>
+      <c r="H22" s="5">
         <v>45170</v>
       </c>
       <c r="I22" s="2">
@@ -2489,29 +2655,31 @@
       <c r="J22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K22" s="6">
+      <c r="K22" s="5">
         <v>40787</v>
       </c>
-      <c r="L22" s="6">
+      <c r="L22" s="5">
         <v>33788</v>
       </c>
-      <c r="M22" s="6">
+      <c r="M22" s="5">
         <v>54271</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="O22" s="6">
+        <v>141</v>
+      </c>
+      <c r="O22" s="5">
         <v>46861</v>
       </c>
-      <c r="S22" s="3"/>
+      <c r="P22" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="C23" s="2">
         <v>45738</v>
@@ -2522,13 +2690,13 @@
       <c r="E23" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>88</v>
+      <c r="F23" s="7" t="s">
+        <v>143</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H23" s="6">
+        <v>144</v>
+      </c>
+      <c r="H23" s="5">
         <v>45474</v>
       </c>
       <c r="I23" s="2">
@@ -2537,35 +2705,40 @@
       <c r="J23" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K23" s="6">
+      <c r="K23" s="5">
         <v>35490</v>
       </c>
-      <c r="L23" s="6">
+      <c r="L23" s="5">
         <v>26954</v>
       </c>
-      <c r="M23" s="6">
+      <c r="M23" s="5">
         <v>47423</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="O23" s="6">
+        <v>145</v>
+      </c>
+      <c r="O23" s="5">
         <v>46010</v>
       </c>
+      <c r="P23" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q23" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="R23" s="6">
+        <v>146</v>
+      </c>
+      <c r="R23" s="5">
         <v>47324</v>
       </c>
-      <c r="S23" s="3"/>
+      <c r="S23" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="24" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="C24" s="2">
         <v>49646</v>
@@ -2576,13 +2749,13 @@
       <c r="E24" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>91</v>
+      <c r="F24" s="7" t="s">
+        <v>148</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H24" s="6">
+        <v>144</v>
+      </c>
+      <c r="H24" s="5">
         <v>45823</v>
       </c>
       <c r="I24" s="2">
@@ -2591,23 +2764,31 @@
       <c r="J24" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K24" s="6">
-        <v>43040</v>
-      </c>
-      <c r="L24" s="6">
+      <c r="K24" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L24" s="5">
         <v>30845</v>
       </c>
-      <c r="M24" s="6">
+      <c r="M24" s="5">
         <v>51318</v>
       </c>
-      <c r="S24" s="3"/>
+      <c r="N24" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="O24" s="5">
+        <v>46973</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="25" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>92</v>
+        <v>150</v>
       </c>
       <c r="C25" s="2">
         <v>53506</v>
@@ -2618,13 +2799,13 @@
       <c r="E25" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>93</v>
+      <c r="F25" s="7" t="s">
+        <v>151</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H25" s="6">
+        <v>144</v>
+      </c>
+      <c r="H25" s="5">
         <v>45915</v>
       </c>
       <c r="I25" s="2">
@@ -2633,29 +2814,31 @@
       <c r="J25" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K25" s="6">
+      <c r="K25" s="5">
         <v>39814</v>
       </c>
-      <c r="L25" s="6">
+      <c r="L25" s="5">
         <v>32347</v>
       </c>
-      <c r="M25" s="6">
+      <c r="M25" s="5">
         <v>52810</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="O25" s="6">
+        <v>152</v>
+      </c>
+      <c r="O25" s="5">
         <v>46610</v>
       </c>
-      <c r="S25" s="3"/>
+      <c r="P25" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>94</v>
+        <v>153</v>
       </c>
       <c r="C26" s="2">
         <v>69375</v>
@@ -2666,14 +2849,14 @@
       <c r="E26" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>95</v>
+      <c r="F26" s="7" t="s">
+        <v>154</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H26" s="6">
-        <v>44927</v>
+        <v>144</v>
+      </c>
+      <c r="H26" s="5">
+        <v>44727</v>
       </c>
       <c r="I26" s="2">
         <v>5</v>
@@ -2681,23 +2864,31 @@
       <c r="J26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K26" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L26" s="6">
-        <v>34861</v>
-      </c>
-      <c r="M26" s="6">
-        <v>55335</v>
-      </c>
-      <c r="S26" s="3"/>
+      <c r="K26" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L26" s="5">
+        <v>35009</v>
+      </c>
+      <c r="M26" s="5">
+        <v>55488</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="O26" s="5">
+        <v>46305</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>96</v>
+        <v>156</v>
       </c>
       <c r="C27" s="2">
         <v>69338</v>
@@ -2708,13 +2899,13 @@
       <c r="E27" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>95</v>
+      <c r="F27" s="7" t="s">
+        <v>154</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H27" s="6">
+        <v>144</v>
+      </c>
+      <c r="H27" s="5">
         <v>45474</v>
       </c>
       <c r="I27" s="2">
@@ -2723,29 +2914,31 @@
       <c r="J27" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K27" s="6">
+      <c r="K27" s="5">
         <v>42562</v>
       </c>
-      <c r="L27" s="6">
+      <c r="L27" s="5">
         <v>31887</v>
       </c>
-      <c r="M27" s="6">
+      <c r="M27" s="5">
         <v>52352</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="O27" s="6">
+        <v>157</v>
+      </c>
+      <c r="O27" s="5">
         <v>46259</v>
       </c>
-      <c r="S27" s="3"/>
+      <c r="P27" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>97</v>
+        <v>158</v>
       </c>
       <c r="C28" s="2">
         <v>59104</v>
@@ -2756,13 +2949,13 @@
       <c r="E28" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>95</v>
+      <c r="F28" s="7" t="s">
+        <v>154</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H28" s="6">
+        <v>144</v>
+      </c>
+      <c r="H28" s="5">
         <v>45474</v>
       </c>
       <c r="I28" s="2">
@@ -2771,29 +2964,31 @@
       <c r="J28" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K28" s="6">
+      <c r="K28" s="5">
         <v>40575</v>
       </c>
-      <c r="L28" s="6">
+      <c r="L28" s="5">
         <v>28894</v>
       </c>
-      <c r="M28" s="6">
+      <c r="M28" s="5">
         <v>49369</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="O28" s="6">
+        <v>159</v>
+      </c>
+      <c r="O28" s="5">
         <v>46011</v>
       </c>
-      <c r="S28" s="3"/>
+      <c r="P28" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>98</v>
+        <v>160</v>
       </c>
       <c r="C29" s="2">
         <v>71341</v>
@@ -2804,13 +2999,13 @@
       <c r="E29" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F29" s="4" t="s">
-        <v>99</v>
+      <c r="F29" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H29" s="6">
+        <v>144</v>
+      </c>
+      <c r="H29" s="5">
         <v>45170</v>
       </c>
       <c r="I29" s="2">
@@ -2819,28 +3014,31 @@
       <c r="J29" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K29" s="6">
+      <c r="K29" s="5">
         <v>43075</v>
       </c>
-      <c r="L29" s="6">
+      <c r="L29" s="5">
         <v>34173</v>
       </c>
-      <c r="M29" s="6">
+      <c r="M29" s="5">
         <v>54636</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="O29" s="6">
+        <v>162</v>
+      </c>
+      <c r="O29" s="5">
         <v>46574</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>100</v>
+        <v>163</v>
       </c>
       <c r="C30" s="2">
         <v>70294</v>
@@ -2851,13 +3049,13 @@
       <c r="E30" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F30" s="4" t="s">
-        <v>99</v>
+      <c r="F30" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H30" s="6">
+        <v>144</v>
+      </c>
+      <c r="H30" s="5">
         <v>45627</v>
       </c>
       <c r="I30" s="2">
@@ -2866,29 +3064,31 @@
       <c r="J30" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K30" s="6">
-        <v>42380</v>
-      </c>
-      <c r="L30" s="6">
+      <c r="K30" s="5">
+        <v>42675</v>
+      </c>
+      <c r="L30" s="5">
         <v>34263</v>
       </c>
-      <c r="M30" s="6">
+      <c r="M30" s="5">
         <v>54728</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="O30" s="6">
+        <v>164</v>
+      </c>
+      <c r="O30" s="5">
         <v>46407</v>
       </c>
-      <c r="S30" s="3"/>
+      <c r="P30" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>101</v>
+        <v>165</v>
       </c>
       <c r="C31" s="2">
         <v>71354</v>
@@ -2899,13 +3099,13 @@
       <c r="E31" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>99</v>
+      <c r="F31" s="7" t="s">
+        <v>161</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H31" s="6">
+        <v>144</v>
+      </c>
+      <c r="H31" s="5">
         <v>45870</v>
       </c>
       <c r="I31" s="2">
@@ -2914,29 +3114,31 @@
       <c r="J31" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K31" s="6">
-        <v>42898</v>
-      </c>
-      <c r="L31" s="6">
-        <v>35947</v>
-      </c>
-      <c r="M31" s="6">
-        <v>56431</v>
+      <c r="K31" s="5">
+        <v>43075</v>
+      </c>
+      <c r="L31" s="5">
+        <v>35801</v>
+      </c>
+      <c r="M31" s="5">
+        <v>56281</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="O31" s="6">
+        <v>166</v>
+      </c>
+      <c r="O31" s="5">
         <v>46574</v>
       </c>
-      <c r="S31" s="3"/>
+      <c r="P31" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>102</v>
+        <v>167</v>
       </c>
       <c r="C32" s="2">
         <v>45787</v>
@@ -2947,13 +3149,13 @@
       <c r="E32" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>103</v>
+      <c r="F32" s="7" t="s">
+        <v>168</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H32" s="6">
+        <v>169</v>
+      </c>
+      <c r="H32" s="5">
         <v>45717</v>
       </c>
       <c r="I32" s="2">
@@ -2962,23 +3164,31 @@
       <c r="J32" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K32" s="6">
+      <c r="K32" s="5">
         <v>35490</v>
       </c>
-      <c r="L32" s="6">
-        <v>46085</v>
-      </c>
-      <c r="M32" s="6">
-        <v>20455</v>
-      </c>
-      <c r="S32" s="3"/>
+      <c r="L32" s="5">
+        <v>28398</v>
+      </c>
+      <c r="M32" s="5">
+        <v>48853</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="O32" s="5">
+        <v>47005</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="33" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>105</v>
+        <v>171</v>
       </c>
       <c r="C33" s="2">
         <v>55301</v>
@@ -2989,13 +3199,13 @@
       <c r="E33" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F33" s="4" t="s">
-        <v>106</v>
+      <c r="F33" s="7" t="s">
+        <v>172</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H33" s="6">
+        <v>169</v>
+      </c>
+      <c r="H33" s="5">
         <v>45627</v>
       </c>
       <c r="I33" s="2">
@@ -3004,29 +3214,31 @@
       <c r="J33" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K33" s="6">
+      <c r="K33" s="5">
         <v>40163</v>
       </c>
-      <c r="L33" s="6">
+      <c r="L33" s="5">
         <v>31639</v>
       </c>
-      <c r="M33" s="6">
+      <c r="M33" s="5">
         <v>52110</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="O33" s="6">
+        <v>173</v>
+      </c>
+      <c r="O33" s="5">
         <v>47324</v>
       </c>
-      <c r="S33" s="3"/>
+      <c r="P33" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="34" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>107</v>
+        <v>174</v>
       </c>
       <c r="C34" s="2">
         <v>55427</v>
@@ -3037,13 +3249,13 @@
       <c r="E34" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F34" s="4" t="s">
-        <v>108</v>
+      <c r="F34" s="7" t="s">
+        <v>175</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H34" s="6">
+        <v>169</v>
+      </c>
+      <c r="H34" s="5">
         <v>45915</v>
       </c>
       <c r="I34" s="2">
@@ -3052,29 +3264,31 @@
       <c r="J34" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K34" s="6">
+      <c r="K34" s="5">
         <v>40163</v>
       </c>
-      <c r="L34" s="6">
+      <c r="L34" s="5">
         <v>32764</v>
       </c>
-      <c r="M34" s="6">
+      <c r="M34" s="5">
         <v>53236</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="O34" s="6">
+        <v>176</v>
+      </c>
+      <c r="O34" s="5">
         <v>46937</v>
       </c>
-      <c r="S34" s="3"/>
+      <c r="P34" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>109</v>
+        <v>177</v>
       </c>
       <c r="C35" s="2">
         <v>75002</v>
@@ -3085,13 +3299,13 @@
       <c r="E35" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F35" s="4" t="s">
-        <v>110</v>
+      <c r="F35" s="7" t="s">
+        <v>178</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H35" s="6">
+        <v>169</v>
+      </c>
+      <c r="H35" s="5">
         <v>45870</v>
       </c>
       <c r="I35" s="2">
@@ -3100,22 +3314,22 @@
       <c r="J35" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K35" s="6">
+      <c r="K35" s="5">
         <v>44866</v>
       </c>
-      <c r="L35" s="6">
+      <c r="L35" s="5">
         <v>35789</v>
       </c>
-      <c r="M35" s="6">
+      <c r="M35" s="5">
         <v>56250</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>111</v>
+        <v>179</v>
       </c>
       <c r="C36" s="2">
         <v>69336</v>
@@ -3126,13 +3340,13 @@
       <c r="E36" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>110</v>
+      <c r="F36" s="7" t="s">
+        <v>178</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H36" s="6">
+        <v>169</v>
+      </c>
+      <c r="H36" s="5">
         <v>45474</v>
       </c>
       <c r="I36" s="2">
@@ -3141,23 +3355,31 @@
       <c r="J36" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K36" s="6">
+      <c r="K36" s="5">
         <v>42562</v>
       </c>
-      <c r="L36" s="6">
-        <v>33929</v>
-      </c>
-      <c r="M36" s="6">
+      <c r="L36" s="5">
+        <v>33928</v>
+      </c>
+      <c r="M36" s="5">
         <v>54393</v>
       </c>
-      <c r="S36" s="3"/>
+      <c r="N36" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="O36" s="5">
+        <v>46246</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>112</v>
+        <v>181</v>
       </c>
       <c r="C37" s="2">
         <v>75315</v>
@@ -3168,13 +3390,13 @@
       <c r="E37" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F37" s="4" t="s">
-        <v>110</v>
+      <c r="F37" s="7" t="s">
+        <v>178</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H37" s="6">
+        <v>169</v>
+      </c>
+      <c r="H37" s="5">
         <v>45536</v>
       </c>
       <c r="I37" s="2">
@@ -3183,29 +3405,31 @@
       <c r="J37" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K37" s="6">
+      <c r="K37" s="5">
         <v>44958</v>
       </c>
-      <c r="L37" s="6">
+      <c r="L37" s="5">
         <v>36752</v>
       </c>
-      <c r="M37" s="6">
+      <c r="M37" s="5">
         <v>57224</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="O37" s="6">
+        <v>182</v>
+      </c>
+      <c r="O37" s="5">
         <v>47114</v>
       </c>
-      <c r="S37" s="3"/>
+      <c r="P37" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>113</v>
+        <v>183</v>
       </c>
       <c r="C38" s="2">
         <v>69369</v>
@@ -3216,14 +3440,14 @@
       <c r="E38" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>114</v>
+      <c r="F38" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H38" s="6">
-        <v>44927</v>
+        <v>169</v>
+      </c>
+      <c r="H38" s="5">
+        <v>44727</v>
       </c>
       <c r="I38" s="2">
         <v>5</v>
@@ -3231,29 +3455,31 @@
       <c r="J38" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K38" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L38" s="6">
+      <c r="K38" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L38" s="5">
         <v>32953</v>
       </c>
-      <c r="M38" s="6">
+      <c r="M38" s="5">
         <v>53418</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="O38" s="6">
+        <v>185</v>
+      </c>
+      <c r="O38" s="5">
         <v>46259</v>
       </c>
-      <c r="S38" s="3"/>
+      <c r="P38" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>115</v>
+        <v>186</v>
       </c>
       <c r="C39" s="2">
         <v>74558</v>
@@ -3264,13 +3490,13 @@
       <c r="E39" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F39" s="4" t="s">
-        <v>114</v>
+      <c r="F39" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="H39" s="6">
+        <v>169</v>
+      </c>
+      <c r="H39" s="5">
         <v>45839</v>
       </c>
       <c r="I39" s="2">
@@ -3279,29 +3505,31 @@
       <c r="J39" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K39" s="6">
+      <c r="K39" s="5">
         <v>44866</v>
       </c>
-      <c r="L39" s="6">
+      <c r="L39" s="5">
         <v>36516</v>
       </c>
-      <c r="M39" s="6">
+      <c r="M39" s="5">
         <v>56980</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="O39" s="6">
+        <v>187</v>
+      </c>
+      <c r="O39" s="5">
         <v>47324</v>
       </c>
-      <c r="S39" s="3"/>
+      <c r="P39" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>116</v>
+        <v>188</v>
       </c>
       <c r="C40" s="2">
         <v>46342</v>
@@ -3312,13 +3540,13 @@
       <c r="E40" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F40" s="4" t="s">
-        <v>117</v>
+      <c r="F40" s="7" t="s">
+        <v>189</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H40" s="6">
+        <v>190</v>
+      </c>
+      <c r="H40" s="5">
         <v>45823</v>
       </c>
       <c r="I40" s="2">
@@ -3327,35 +3555,40 @@
       <c r="J40" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K40" s="6">
+      <c r="K40" s="5">
         <v>35490</v>
       </c>
-      <c r="L40" s="6">
+      <c r="L40" s="5">
         <v>28725</v>
       </c>
-      <c r="M40" s="6">
+      <c r="M40" s="5">
         <v>49188</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="O40" s="6">
+        <v>191</v>
+      </c>
+      <c r="O40" s="5">
         <v>47324</v>
       </c>
+      <c r="P40" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q40" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="R40" s="6">
+        <v>192</v>
+      </c>
+      <c r="R40" s="5">
         <v>47114</v>
       </c>
-      <c r="S40" s="3"/>
+      <c r="S40" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="41" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>119</v>
+        <v>193</v>
       </c>
       <c r="C41" s="2">
         <v>55390</v>
@@ -3366,13 +3599,13 @@
       <c r="E41" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F41" s="4" t="s">
-        <v>120</v>
+      <c r="F41" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H41" s="6">
+        <v>190</v>
+      </c>
+      <c r="H41" s="5">
         <v>45717</v>
       </c>
       <c r="I41" s="2">
@@ -3381,22 +3614,31 @@
       <c r="J41" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K41" s="6">
+      <c r="K41" s="5">
         <v>40163</v>
       </c>
-      <c r="L41" s="6">
+      <c r="L41" s="5">
         <v>32343</v>
       </c>
-      <c r="M41" s="6">
+      <c r="M41" s="5">
         <v>52810</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="O41" s="5">
+        <v>46837</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>121</v>
+        <v>196</v>
       </c>
       <c r="C42" s="2">
         <v>58164</v>
@@ -3407,13 +3649,13 @@
       <c r="E42" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F42" s="4" t="s">
-        <v>122</v>
+      <c r="F42" s="7" t="s">
+        <v>197</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H42" s="6">
+        <v>190</v>
+      </c>
+      <c r="H42" s="5">
         <v>45275</v>
       </c>
       <c r="I42" s="2">
@@ -3422,29 +3664,31 @@
       <c r="J42" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K42" s="6">
-        <v>40182</v>
-      </c>
-      <c r="L42" s="6">
+      <c r="K42" s="5">
+        <v>40269</v>
+      </c>
+      <c r="L42" s="5">
         <v>30433</v>
       </c>
-      <c r="M42" s="6">
+      <c r="M42" s="5">
         <v>50891</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="O42" s="6">
+        <v>198</v>
+      </c>
+      <c r="O42" s="5">
         <v>47203</v>
       </c>
-      <c r="S42" s="3"/>
+      <c r="P42" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>123</v>
+        <v>199</v>
       </c>
       <c r="C43" s="2">
         <v>59093</v>
@@ -3455,13 +3699,13 @@
       <c r="E43" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F43" s="4" t="s">
-        <v>124</v>
+      <c r="F43" s="7" t="s">
+        <v>200</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H43" s="6">
+        <v>190</v>
+      </c>
+      <c r="H43" s="5">
         <v>45474</v>
       </c>
       <c r="I43" s="2">
@@ -3470,29 +3714,31 @@
       <c r="J43" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K43" s="6">
+      <c r="K43" s="5">
         <v>40575</v>
       </c>
-      <c r="L43" s="6">
+      <c r="L43" s="5">
         <v>29922</v>
       </c>
-      <c r="M43" s="6">
+      <c r="M43" s="5">
         <v>50406</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="O43" s="6">
+        <v>201</v>
+      </c>
+      <c r="O43" s="5">
         <v>47114</v>
       </c>
-      <c r="S43" s="3"/>
+      <c r="P43" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>125</v>
+        <v>202</v>
       </c>
       <c r="C44" s="2">
         <v>59097</v>
@@ -3503,13 +3749,13 @@
       <c r="E44" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F44" s="4" t="s">
-        <v>124</v>
+      <c r="F44" s="7" t="s">
+        <v>200</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H44" s="6">
+        <v>190</v>
+      </c>
+      <c r="H44" s="5">
         <v>45474</v>
       </c>
       <c r="I44" s="2">
@@ -3518,29 +3764,31 @@
       <c r="J44" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K44" s="6">
+      <c r="K44" s="5">
         <v>40575</v>
       </c>
-      <c r="L44" s="6">
+      <c r="L44" s="5">
         <v>31868</v>
       </c>
-      <c r="M44" s="6">
+      <c r="M44" s="5">
         <v>52352</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="O44" s="6">
+        <v>203</v>
+      </c>
+      <c r="O44" s="5">
         <v>47114</v>
       </c>
-      <c r="S44" s="3"/>
+      <c r="P44" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>126</v>
+        <v>204</v>
       </c>
       <c r="C45" s="2">
         <v>48219</v>
@@ -3551,13 +3799,13 @@
       <c r="E45" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F45" s="4" t="s">
-        <v>127</v>
+      <c r="F45" s="7" t="s">
+        <v>205</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H45" s="6">
+        <v>190</v>
+      </c>
+      <c r="H45" s="5">
         <v>45627</v>
       </c>
       <c r="I45" s="2">
@@ -3566,23 +3814,31 @@
       <c r="J45" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K45" s="6">
+      <c r="K45" s="5">
         <v>37135</v>
       </c>
-      <c r="L45" s="6">
+      <c r="L45" s="5">
         <v>27832</v>
       </c>
-      <c r="M45" s="6">
+      <c r="M45" s="5">
         <v>48305</v>
       </c>
-      <c r="S45" s="3"/>
+      <c r="N45" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="O45" s="5">
+        <v>47097</v>
+      </c>
+      <c r="P45" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A46" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>128</v>
+        <v>207</v>
       </c>
       <c r="C46" s="2">
         <v>70804</v>
@@ -3593,13 +3849,13 @@
       <c r="E46" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F46" s="4" t="s">
-        <v>127</v>
+      <c r="F46" s="7" t="s">
+        <v>205</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H46" s="6">
+        <v>190</v>
+      </c>
+      <c r="H46" s="5">
         <v>45627</v>
       </c>
       <c r="I46" s="2">
@@ -3608,23 +3864,31 @@
       <c r="J46" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K46" s="6">
+      <c r="K46" s="5">
         <v>42725</v>
       </c>
-      <c r="L46" s="6">
+      <c r="L46" s="5">
         <v>35155</v>
       </c>
-      <c r="M46" s="6">
+      <c r="M46" s="5">
         <v>55610</v>
       </c>
-      <c r="S46" s="3"/>
+      <c r="N46" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="O46" s="5">
+        <v>46448</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A47" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>129</v>
+        <v>209</v>
       </c>
       <c r="C47" s="2">
         <v>70292</v>
@@ -3635,14 +3899,14 @@
       <c r="E47" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F47" s="4" t="s">
-        <v>127</v>
+      <c r="F47" s="7" t="s">
+        <v>205</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H47" s="6">
-        <v>44927</v>
+        <v>190</v>
+      </c>
+      <c r="H47" s="5">
+        <v>44727</v>
       </c>
       <c r="I47" s="2">
         <v>5</v>
@@ -3650,29 +3914,31 @@
       <c r="J47" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K47" s="6">
-        <v>42380</v>
-      </c>
-      <c r="L47" s="6">
+      <c r="K47" s="5">
+        <v>42675</v>
+      </c>
+      <c r="L47" s="5">
         <v>34751</v>
       </c>
-      <c r="M47" s="6">
+      <c r="M47" s="5">
         <v>55213</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="O47" s="6">
+        <v>210</v>
+      </c>
+      <c r="O47" s="5">
         <v>46259</v>
       </c>
-      <c r="S47" s="3"/>
+      <c r="P47" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>130</v>
+        <v>211</v>
       </c>
       <c r="C48" s="2">
         <v>44515</v>
@@ -3683,13 +3949,13 @@
       <c r="E48" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F48" s="4" t="s">
-        <v>131</v>
+      <c r="F48" s="7" t="s">
+        <v>212</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H48" s="6">
+        <v>213</v>
+      </c>
+      <c r="H48" s="5">
         <v>45823</v>
       </c>
       <c r="I48" s="2">
@@ -3698,36 +3964,40 @@
       <c r="J48" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K48" s="6">
+      <c r="K48" s="5">
         <v>35217</v>
       </c>
-      <c r="L48" s="6">
+      <c r="L48" s="5">
         <v>26900</v>
       </c>
-      <c r="M48" s="6">
+      <c r="M48" s="5">
         <v>47362</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="O48" s="6">
+        <v>214</v>
+      </c>
+      <c r="O48" s="5">
         <v>47005</v>
       </c>
-      <c r="P48" s="3"/>
+      <c r="P48" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q48" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="R48" s="6">
+        <v>215</v>
+      </c>
+      <c r="R48" s="5">
         <v>47324</v>
       </c>
-      <c r="S48" s="3"/>
+      <c r="S48" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="49" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A49" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>133</v>
+        <v>216</v>
       </c>
       <c r="C49" s="2">
         <v>53572</v>
@@ -3738,13 +4008,13 @@
       <c r="E49" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F49" s="4" t="s">
-        <v>134</v>
+      <c r="F49" s="7" t="s">
+        <v>217</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H49" s="6">
+        <v>213</v>
+      </c>
+      <c r="H49" s="5">
         <v>45566</v>
       </c>
       <c r="I49" s="2">
@@ -3753,24 +4023,31 @@
       <c r="J49" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K49" s="6">
+      <c r="K49" s="5">
         <v>39814</v>
       </c>
-      <c r="L49" s="6">
-        <v>33062</v>
-      </c>
-      <c r="M49" s="6">
-        <v>53540</v>
-      </c>
-      <c r="P49" s="3"/>
-      <c r="S49" s="3"/>
+      <c r="L49" s="5">
+        <v>33092</v>
+      </c>
+      <c r="M49" s="5">
+        <v>53571</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="O49" s="5">
+        <v>46610</v>
+      </c>
+      <c r="P49" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="50" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A50" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>135</v>
+        <v>219</v>
       </c>
       <c r="C50" s="2">
         <v>50474</v>
@@ -3781,13 +4058,13 @@
       <c r="E50" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F50" s="4" t="s">
-        <v>136</v>
+      <c r="F50" s="7" t="s">
+        <v>220</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H50" s="6">
+        <v>213</v>
+      </c>
+      <c r="H50" s="5">
         <v>45962</v>
       </c>
       <c r="I50" s="2">
@@ -3796,30 +4073,31 @@
       <c r="J50" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K50" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L50" s="6">
+      <c r="K50" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L50" s="5">
         <v>32677</v>
       </c>
-      <c r="M50" s="6">
+      <c r="M50" s="5">
         <v>53144</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="O50" s="6">
+        <v>221</v>
+      </c>
+      <c r="O50" s="5">
         <v>47324</v>
       </c>
-      <c r="P50" s="3"/>
-      <c r="S50" s="3"/>
+      <c r="P50" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A51" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>137</v>
+        <v>222</v>
       </c>
       <c r="C51" s="2">
         <v>62265</v>
@@ -3830,13 +4108,13 @@
       <c r="E51" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F51" s="4" t="s">
-        <v>138</v>
+      <c r="F51" s="7" t="s">
+        <v>223</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H51" s="6">
+        <v>213</v>
+      </c>
+      <c r="H51" s="5">
         <v>45536</v>
       </c>
       <c r="I51" s="2">
@@ -3845,30 +4123,31 @@
       <c r="J51" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K51" s="6">
+      <c r="K51" s="5">
         <v>41153</v>
       </c>
-      <c r="L51" s="6">
+      <c r="L51" s="5">
         <v>32982</v>
       </c>
-      <c r="M51" s="6">
+      <c r="M51" s="5">
         <v>53448</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="O51" s="6">
+        <v>224</v>
+      </c>
+      <c r="O51" s="5">
         <v>46881</v>
       </c>
-      <c r="P51" s="3"/>
-      <c r="S51" s="3"/>
+      <c r="P51" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A52" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>139</v>
+        <v>225</v>
       </c>
       <c r="C52" s="2">
         <v>69379</v>
@@ -3879,14 +4158,14 @@
       <c r="E52" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F52" s="4" t="s">
-        <v>138</v>
+      <c r="F52" s="7" t="s">
+        <v>223</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H52" s="6">
-        <v>44927</v>
+        <v>213</v>
+      </c>
+      <c r="H52" s="5">
+        <v>44727</v>
       </c>
       <c r="I52" s="2">
         <v>5</v>
@@ -3894,24 +4173,31 @@
       <c r="J52" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K52" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L52" s="6">
-        <v>33889</v>
-      </c>
-      <c r="M52" s="6">
-        <v>54363</v>
-      </c>
-      <c r="P52" s="3"/>
-      <c r="S52" s="3"/>
+      <c r="K52" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L52" s="5">
+        <v>33948</v>
+      </c>
+      <c r="M52" s="5">
+        <v>54424</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="O52" s="5">
+        <v>46448</v>
+      </c>
+      <c r="P52" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A53" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>140</v>
+        <v>227</v>
       </c>
       <c r="C53" s="2">
         <v>70290</v>
@@ -3922,13 +4208,13 @@
       <c r="E53" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F53" s="4" t="s">
-        <v>141</v>
+      <c r="F53" s="7" t="s">
+        <v>228</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H53" s="6">
+        <v>213</v>
+      </c>
+      <c r="H53" s="5">
         <v>45474</v>
       </c>
       <c r="I53" s="2">
@@ -3937,30 +4223,31 @@
       <c r="J53" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K53" s="6">
+      <c r="K53" s="5">
         <v>42675</v>
       </c>
-      <c r="L53" s="6">
+      <c r="L53" s="5">
         <v>35066</v>
       </c>
-      <c r="M53" s="6">
+      <c r="M53" s="5">
         <v>55550</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="O53" s="6">
+        <v>229</v>
+      </c>
+      <c r="O53" s="5">
         <v>46595</v>
       </c>
-      <c r="P53" s="3"/>
-      <c r="S53" s="3"/>
+      <c r="P53" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A54" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>142</v>
+        <v>230</v>
       </c>
       <c r="C54" s="2">
         <v>71359</v>
@@ -3971,13 +4258,13 @@
       <c r="E54" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F54" s="4" t="s">
-        <v>141</v>
+      <c r="F54" s="7" t="s">
+        <v>228</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H54" s="6">
+        <v>213</v>
+      </c>
+      <c r="H54" s="5">
         <v>45962</v>
       </c>
       <c r="I54" s="2">
@@ -3986,30 +4273,31 @@
       <c r="J54" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K54" s="6">
-        <v>42898</v>
-      </c>
-      <c r="L54" s="6">
+      <c r="K54" s="5">
+        <v>43075</v>
+      </c>
+      <c r="L54" s="5">
         <v>34226</v>
       </c>
-      <c r="M54" s="6">
+      <c r="M54" s="5">
         <v>54697</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="O54" s="6">
+        <v>231</v>
+      </c>
+      <c r="O54" s="5">
         <v>46574</v>
       </c>
-      <c r="P54" s="3"/>
-      <c r="S54" s="3"/>
+      <c r="P54" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A55" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>143</v>
+        <v>232</v>
       </c>
       <c r="C55" s="2">
         <v>70295</v>
@@ -4020,13 +4308,13 @@
       <c r="E55" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F55" s="4" t="s">
-        <v>141</v>
+      <c r="F55" s="7" t="s">
+        <v>228</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="H55" s="6">
+        <v>213</v>
+      </c>
+      <c r="H55" s="5">
         <v>45474</v>
       </c>
       <c r="I55" s="2">
@@ -4035,30 +4323,31 @@
       <c r="J55" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K55" s="6">
+      <c r="K55" s="5">
         <v>42675</v>
       </c>
-      <c r="L55" s="6">
+      <c r="L55" s="5">
         <v>34439</v>
       </c>
-      <c r="M55" s="6">
+      <c r="M55" s="5">
         <v>54909</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="O55" s="6">
+        <v>233</v>
+      </c>
+      <c r="O55" s="5">
         <v>46595</v>
       </c>
-      <c r="P55" s="3"/>
-      <c r="S55" s="3"/>
+      <c r="P55" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A56" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>144</v>
+        <v>234</v>
       </c>
       <c r="C56" s="2">
         <v>45770</v>
@@ -4069,13 +4358,13 @@
       <c r="E56" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F56" s="4" t="s">
-        <v>145</v>
+      <c r="F56" s="7" t="s">
+        <v>235</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H56" s="6">
+        <v>236</v>
+      </c>
+      <c r="H56" s="5">
         <v>45611</v>
       </c>
       <c r="I56" s="2">
@@ -4084,36 +4373,40 @@
       <c r="J56" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K56" s="6">
+      <c r="K56" s="5">
         <v>35490</v>
       </c>
-      <c r="L56" s="6">
+      <c r="L56" s="5">
         <v>28038</v>
       </c>
-      <c r="M56" s="6">
+      <c r="M56" s="5">
         <v>48519</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="O56" s="6">
+        <v>237</v>
+      </c>
+      <c r="O56" s="5">
         <v>47009</v>
       </c>
-      <c r="P56" s="3"/>
+      <c r="P56" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q56" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="R56" s="6">
+        <v>238</v>
+      </c>
+      <c r="R56" s="5">
         <v>47232</v>
       </c>
-      <c r="S56" s="3"/>
+      <c r="S56" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="57" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A57" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>147</v>
+        <v>239</v>
       </c>
       <c r="C57" s="2">
         <v>50419</v>
@@ -4124,13 +4417,13 @@
       <c r="E57" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F57" s="4" t="s">
-        <v>148</v>
+      <c r="F57" s="7" t="s">
+        <v>240</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H57" s="6">
+        <v>236</v>
+      </c>
+      <c r="H57" s="5">
         <v>45915</v>
       </c>
       <c r="I57" s="2">
@@ -4139,24 +4432,31 @@
       <c r="J57" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K57" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L57" s="6">
-        <v>32724</v>
-      </c>
-      <c r="M57" s="6">
-        <v>53206</v>
-      </c>
-      <c r="P57" s="3"/>
-      <c r="S57" s="3"/>
+      <c r="K57" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L57" s="5">
+        <v>32606</v>
+      </c>
+      <c r="M57" s="5">
+        <v>53083</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="O57" s="5">
+        <v>47261</v>
+      </c>
+      <c r="P57" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="58" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A58" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>149</v>
+        <v>242</v>
       </c>
       <c r="C58" s="2">
         <v>48461</v>
@@ -4167,13 +4467,13 @@
       <c r="E58" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F58" s="4" t="s">
-        <v>150</v>
+      <c r="F58" s="7" t="s">
+        <v>243</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H58" s="6">
+        <v>236</v>
+      </c>
+      <c r="H58" s="5">
         <v>45823</v>
       </c>
       <c r="I58" s="2">
@@ -4182,30 +4482,31 @@
       <c r="J58" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K58" s="6">
+      <c r="K58" s="5">
         <v>38443</v>
       </c>
-      <c r="L58" s="6">
+      <c r="L58" s="5">
         <v>30300</v>
       </c>
-      <c r="M58" s="6">
+      <c r="M58" s="5">
         <v>50771</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="O58" s="6">
+        <v>244</v>
+      </c>
+      <c r="O58" s="5">
         <v>46937</v>
       </c>
-      <c r="P58" s="3"/>
-      <c r="S58" s="3"/>
+      <c r="P58" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A59" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>151</v>
+        <v>245</v>
       </c>
       <c r="C59" s="2">
         <v>61298</v>
@@ -4216,14 +4517,14 @@
       <c r="E59" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F59" s="4" t="s">
-        <v>152</v>
+      <c r="F59" s="7" t="s">
+        <v>246</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H59" s="6">
-        <v>44927</v>
+        <v>236</v>
+      </c>
+      <c r="H59" s="5">
+        <v>44727</v>
       </c>
       <c r="I59" s="2">
         <v>5</v>
@@ -4231,30 +4532,31 @@
       <c r="J59" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K59" s="6">
-        <v>40552</v>
-      </c>
-      <c r="L59" s="6">
+      <c r="K59" s="5">
+        <v>40787</v>
+      </c>
+      <c r="L59" s="5">
         <v>33350</v>
       </c>
-      <c r="M59" s="6">
+      <c r="M59" s="5">
         <v>53813</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="O59" s="6">
+        <v>247</v>
+      </c>
+      <c r="O59" s="5">
         <v>47232</v>
       </c>
-      <c r="P59" s="3"/>
-      <c r="S59" s="3"/>
+      <c r="P59" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A60" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>153</v>
+        <v>248</v>
       </c>
       <c r="C60" s="2">
         <v>61311</v>
@@ -4265,13 +4567,13 @@
       <c r="E60" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F60" s="4" t="s">
-        <v>152</v>
+      <c r="F60" s="7" t="s">
+        <v>246</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H60" s="6">
+        <v>236</v>
+      </c>
+      <c r="H60" s="5">
         <v>45536</v>
       </c>
       <c r="I60" s="2">
@@ -4280,30 +4582,31 @@
       <c r="J60" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K60" s="6">
+      <c r="K60" s="5">
         <v>40787</v>
       </c>
-      <c r="L60" s="6">
+      <c r="L60" s="5">
         <v>33816</v>
       </c>
-      <c r="M60" s="6">
+      <c r="M60" s="5">
         <v>54271</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="O60" s="6">
+        <v>249</v>
+      </c>
+      <c r="O60" s="5">
         <v>46861</v>
       </c>
-      <c r="P60" s="3"/>
-      <c r="S60" s="3"/>
+      <c r="P60" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A61" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>154</v>
+        <v>250</v>
       </c>
       <c r="C61" s="2">
         <v>69875</v>
@@ -4314,13 +4617,13 @@
       <c r="E61" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F61" s="4" t="s">
-        <v>152</v>
+      <c r="F61" s="7" t="s">
+        <v>246</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H61" s="6">
+        <v>236</v>
+      </c>
+      <c r="H61" s="5">
         <v>45627</v>
       </c>
       <c r="I61" s="2">
@@ -4329,30 +4632,31 @@
       <c r="J61" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K61" s="6">
+      <c r="K61" s="5">
         <v>42597</v>
       </c>
-      <c r="L61" s="6">
-        <v>35309</v>
-      </c>
-      <c r="M61" s="6">
-        <v>55793</v>
+      <c r="L61" s="5">
+        <v>35347</v>
+      </c>
+      <c r="M61" s="5">
+        <v>55824</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="O61" s="6">
+        <v>251</v>
+      </c>
+      <c r="O61" s="5">
         <v>46446</v>
       </c>
-      <c r="P61" s="3"/>
-      <c r="S61" s="3"/>
+      <c r="P61" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A62" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="C62" s="2">
         <v>61303</v>
@@ -4363,13 +4667,13 @@
       <c r="E62" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F62" s="4" t="s">
-        <v>152</v>
+      <c r="F62" s="7" t="s">
+        <v>246</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H62" s="6">
+        <v>236</v>
+      </c>
+      <c r="H62" s="5">
         <v>45474</v>
       </c>
       <c r="I62" s="2">
@@ -4378,30 +4682,31 @@
       <c r="J62" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K62" s="6">
+      <c r="K62" s="5">
         <v>40787</v>
       </c>
-      <c r="L62" s="6">
+      <c r="L62" s="5">
         <v>33698</v>
       </c>
-      <c r="M62" s="6">
+      <c r="M62" s="5">
         <v>54179</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="O62" s="6">
+        <v>253</v>
+      </c>
+      <c r="O62" s="5">
         <v>47097</v>
       </c>
-      <c r="P62" s="3"/>
-      <c r="S62" s="3"/>
+      <c r="P62" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A63" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>156</v>
+        <v>254</v>
       </c>
       <c r="C63" s="2">
         <v>59103</v>
@@ -4412,13 +4717,13 @@
       <c r="E63" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F63" s="4" t="s">
-        <v>157</v>
+      <c r="F63" s="7" t="s">
+        <v>255</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H63" s="6">
+        <v>236</v>
+      </c>
+      <c r="H63" s="5">
         <v>45474</v>
       </c>
       <c r="I63" s="2">
@@ -4427,30 +4732,31 @@
       <c r="J63" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K63" s="6">
+      <c r="K63" s="5">
         <v>40575</v>
       </c>
-      <c r="L63" s="6">
+      <c r="L63" s="5">
         <v>30379</v>
       </c>
-      <c r="M63" s="6">
+      <c r="M63" s="5">
         <v>50861</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="O63" s="6">
+        <v>256</v>
+      </c>
+      <c r="O63" s="5">
         <v>47097</v>
       </c>
-      <c r="P63" s="3"/>
-      <c r="S63" s="3"/>
+      <c r="P63" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A64" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>158</v>
+        <v>257</v>
       </c>
       <c r="C64" s="2">
         <v>61302</v>
@@ -4461,14 +4767,14 @@
       <c r="E64" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F64" s="4" t="s">
-        <v>157</v>
+      <c r="F64" s="7" t="s">
+        <v>255</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H64" s="6">
-        <v>44927</v>
+        <v>236</v>
+      </c>
+      <c r="H64" s="5">
+        <v>45170</v>
       </c>
       <c r="I64" s="2">
         <v>5</v>
@@ -4476,47 +4782,48 @@
       <c r="J64" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K64" s="6">
-        <v>40552</v>
-      </c>
-      <c r="L64" s="6">
+      <c r="K64" s="5">
+        <v>40787</v>
+      </c>
+      <c r="L64" s="5">
         <v>33850</v>
       </c>
-      <c r="M64" s="6">
-        <v>54332</v>
+      <c r="M64" s="5">
+        <v>54149</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="O64" s="6">
+        <v>258</v>
+      </c>
+      <c r="O64" s="5">
         <v>47097</v>
       </c>
-      <c r="P64" s="3"/>
-      <c r="S64" s="3"/>
+      <c r="P64" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A65" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>159</v>
+        <v>259</v>
       </c>
       <c r="C65" s="2">
         <v>70798</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="D65" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F65" s="4" t="s">
-        <v>157</v>
+      <c r="F65" s="7" t="s">
+        <v>255</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="H65" s="8">
+        <v>236</v>
+      </c>
+      <c r="H65" s="5">
         <v>45474</v>
       </c>
       <c r="I65" s="2">
@@ -4525,47 +4832,48 @@
       <c r="J65" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K65" s="6">
+      <c r="K65" s="5">
         <v>42725</v>
       </c>
-      <c r="L65" s="6">
+      <c r="L65" s="5">
         <v>35628</v>
       </c>
-      <c r="M65" s="6">
+      <c r="M65" s="5">
         <v>56097</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="O65" s="6">
+        <v>260</v>
+      </c>
+      <c r="O65" s="5">
         <v>46259</v>
       </c>
-      <c r="P65" s="3"/>
-      <c r="S65" s="3"/>
+      <c r="P65" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A66" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>160</v>
+        <v>261</v>
       </c>
       <c r="C66" s="2">
         <v>55351</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="D66" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F66" s="4" t="s">
-        <v>161</v>
+      <c r="F66" s="7" t="s">
+        <v>262</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="H66" s="8">
+        <v>263</v>
+      </c>
+      <c r="H66" s="5">
         <v>45731</v>
       </c>
       <c r="I66" s="2">
@@ -4574,47 +4882,39 @@
       <c r="J66" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K66" s="6">
+      <c r="K66" s="5">
         <v>40163</v>
       </c>
-      <c r="L66" s="6">
+      <c r="L66" s="5">
         <v>32371</v>
       </c>
-      <c r="M66" s="6">
+      <c r="M66" s="5">
         <v>52841</v>
       </c>
-      <c r="N66" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="O66" s="6">
-        <v>45810</v>
-      </c>
-      <c r="P66" s="3"/>
-      <c r="S66" s="3"/>
     </row>
     <row r="67" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A67" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>163</v>
+        <v>264</v>
       </c>
       <c r="C67" s="2">
         <v>61304</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D67" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F67" s="4" t="s">
-        <v>164</v>
+      <c r="F67" s="7" t="s">
+        <v>265</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="H67" s="6">
+        <v>263</v>
+      </c>
+      <c r="H67" s="5">
         <v>45915</v>
       </c>
       <c r="I67" s="2">
@@ -4623,47 +4923,48 @@
       <c r="J67" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K67" s="6">
+      <c r="K67" s="5">
         <v>40787</v>
       </c>
-      <c r="L67" s="6">
+      <c r="L67" s="5">
         <v>33746</v>
       </c>
-      <c r="M67" s="6">
+      <c r="M67" s="5">
         <v>54210</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="O67" s="6">
+        <v>266</v>
+      </c>
+      <c r="O67" s="5">
         <v>47054</v>
       </c>
-      <c r="P67" s="3"/>
-      <c r="S67" s="3"/>
+      <c r="P67" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="68" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A68" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>165</v>
+        <v>267</v>
       </c>
       <c r="C68" s="2">
         <v>59096</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D68" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F68" s="4" t="s">
-        <v>166</v>
+      <c r="F68" s="7" t="s">
+        <v>268</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="H68" s="8">
+        <v>263</v>
+      </c>
+      <c r="H68" s="5">
         <v>45731</v>
       </c>
       <c r="I68" s="2">
@@ -4672,47 +4973,48 @@
       <c r="J68" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K68" s="6">
+      <c r="K68" s="5">
         <v>40575</v>
       </c>
-      <c r="L68" s="6">
+      <c r="L68" s="5">
         <v>30740</v>
       </c>
-      <c r="M68" s="6">
+      <c r="M68" s="5">
         <v>51196</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="O68" s="6">
+        <v>269</v>
+      </c>
+      <c r="O68" s="5">
         <v>47054</v>
       </c>
-      <c r="P68" s="3"/>
-      <c r="S68" s="3"/>
+      <c r="P68" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A69" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>167</v>
+        <v>270</v>
       </c>
       <c r="C69" s="2">
         <v>69333</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="D69" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F69" s="4" t="s">
-        <v>168</v>
+      <c r="F69" s="7" t="s">
+        <v>271</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="H69" s="8">
+        <v>263</v>
+      </c>
+      <c r="H69" s="5">
         <v>45748</v>
       </c>
       <c r="I69" s="2">
@@ -4721,47 +5023,48 @@
       <c r="J69" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K69" s="6">
+      <c r="K69" s="5">
         <v>42562</v>
       </c>
-      <c r="L69" s="6">
+      <c r="L69" s="5">
         <v>32525</v>
       </c>
-      <c r="M69" s="6">
+      <c r="M69" s="5">
         <v>52994</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="O69" s="6">
+        <v>272</v>
+      </c>
+      <c r="O69" s="5">
         <v>46259</v>
       </c>
-      <c r="P69" s="3"/>
-      <c r="S69" s="3"/>
+      <c r="P69" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A70" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>169</v>
+        <v>273</v>
       </c>
       <c r="C70" s="2">
         <v>61301</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D70" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F70" s="4" t="s">
-        <v>168</v>
+      <c r="F70" s="7" t="s">
+        <v>271</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="H70" s="6">
+        <v>263</v>
+      </c>
+      <c r="H70" s="5">
         <v>45627</v>
       </c>
       <c r="I70" s="2">
@@ -4770,41 +5073,48 @@
       <c r="J70" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K70" s="6">
-        <v>40552</v>
-      </c>
-      <c r="L70" s="6">
-        <v>33606</v>
-      </c>
-      <c r="M70" s="6">
-        <v>54089</v>
-      </c>
-      <c r="P70" s="3"/>
-      <c r="S70" s="3"/>
+      <c r="K70" s="5">
+        <v>40787</v>
+      </c>
+      <c r="L70" s="5">
+        <v>33664</v>
+      </c>
+      <c r="M70" s="5">
+        <v>54149</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="O70" s="5">
+        <v>47005</v>
+      </c>
+      <c r="P70" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A71" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>170</v>
+        <v>275</v>
       </c>
       <c r="C71" s="2">
         <v>71342</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D71" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F71" s="4" t="s">
-        <v>168</v>
+      <c r="F71" s="7" t="s">
+        <v>271</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="H71" s="6">
+        <v>263</v>
+      </c>
+      <c r="H71" s="5">
         <v>45474</v>
       </c>
       <c r="I71" s="2">
@@ -4813,47 +5123,48 @@
       <c r="J71" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K71" s="6">
+      <c r="K71" s="5">
         <v>43075</v>
       </c>
-      <c r="L71" s="6">
+      <c r="L71" s="5">
         <v>35915</v>
       </c>
-      <c r="M71" s="6">
+      <c r="M71" s="5">
         <v>56370</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="O71" s="6">
+        <v>276</v>
+      </c>
+      <c r="O71" s="5">
         <v>46574</v>
       </c>
-      <c r="P71" s="3"/>
-      <c r="S71" s="3"/>
+      <c r="P71" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A72" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>171</v>
+        <v>277</v>
       </c>
       <c r="C72" s="2">
         <v>48319</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D72" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F72" s="4" t="s">
-        <v>168</v>
+      <c r="F72" s="7" t="s">
+        <v>271</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="H72" s="8">
+        <v>263</v>
+      </c>
+      <c r="H72" s="5">
         <v>45962</v>
       </c>
       <c r="I72" s="2">
@@ -4862,41 +5173,48 @@
       <c r="J72" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K72" s="6">
+      <c r="K72" s="5">
         <v>37135</v>
       </c>
-      <c r="L72" s="6">
+      <c r="L72" s="5">
         <v>30125</v>
       </c>
-      <c r="M72" s="6">
+      <c r="M72" s="5">
         <v>50587</v>
       </c>
-      <c r="P72" s="3"/>
-      <c r="S72" s="3"/>
+      <c r="N72" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="O72" s="5">
+        <v>47114</v>
+      </c>
+      <c r="P72" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A73" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>172</v>
+        <v>279</v>
       </c>
       <c r="C73" s="2">
         <v>74572</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D73" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F73" s="4" t="s">
-        <v>173</v>
+      <c r="F73" s="7" t="s">
+        <v>280</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="H73" s="8">
+        <v>263</v>
+      </c>
+      <c r="H73" s="5">
         <v>45474</v>
       </c>
       <c r="I73" s="2">
@@ -4905,48 +5223,49 @@
       <c r="J73" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K73" s="6">
+      <c r="K73" s="5">
         <v>44866</v>
       </c>
-      <c r="L73" s="6">
-        <v>37697</v>
-      </c>
-      <c r="M73" s="6">
+      <c r="L73" s="5">
+        <v>37758</v>
+      </c>
+      <c r="M73" s="5">
         <v>58166</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="O73" s="6">
+        <v>281</v>
+      </c>
+      <c r="O73" s="5">
         <v>46916</v>
       </c>
-      <c r="P73" s="3"/>
-      <c r="S73" s="3"/>
+      <c r="P73" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A74" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>174</v>
+        <v>282</v>
       </c>
       <c r="C74" s="2">
         <v>76904</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="D74" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F74" s="4" t="s">
-        <v>173</v>
+      <c r="F74" s="7" t="s">
+        <v>280</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="H74" s="8">
-        <v>45659</v>
+        <v>263</v>
+      </c>
+      <c r="H74" s="5">
+        <v>45689</v>
       </c>
       <c r="I74" s="2">
         <v>5</v>
@@ -4954,47 +5273,48 @@
       <c r="J74" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K74" s="6">
+      <c r="K74" s="5">
         <v>45289</v>
       </c>
-      <c r="L74" s="6">
+      <c r="L74" s="5">
         <v>37595</v>
       </c>
-      <c r="M74" s="6">
+      <c r="M74" s="5">
         <v>58076</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="O74" s="6">
+        <v>283</v>
+      </c>
+      <c r="O74" s="5">
         <v>47285</v>
       </c>
-      <c r="P74" s="3"/>
-      <c r="S74" s="3"/>
+      <c r="P74" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A75" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>175</v>
+        <v>284</v>
       </c>
       <c r="C75" s="2">
         <v>55341</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="D75" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F75" s="4" t="s">
-        <v>176</v>
+      <c r="F75" s="7" t="s">
+        <v>285</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="H75" s="8">
+        <v>286</v>
+      </c>
+      <c r="H75" s="5">
         <v>45823</v>
       </c>
       <c r="I75" s="2">
@@ -5003,53 +5323,57 @@
       <c r="J75" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K75" s="6">
+      <c r="K75" s="5">
         <v>40163</v>
       </c>
-      <c r="L75" s="6">
+      <c r="L75" s="5">
         <v>31762</v>
       </c>
-      <c r="M75" s="6">
+      <c r="M75" s="5">
         <v>52232</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="O75" s="6">
+        <v>287</v>
+      </c>
+      <c r="O75" s="5">
         <v>47097</v>
       </c>
-      <c r="P75" s="3"/>
+      <c r="P75" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q75" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="R75" s="6">
+        <v>288</v>
+      </c>
+      <c r="R75" s="5">
         <v>47114</v>
       </c>
-      <c r="S75" s="3"/>
+      <c r="S75" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="76" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A76" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>178</v>
+        <v>289</v>
       </c>
       <c r="C76" s="2">
         <v>59094</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="D76" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F76" s="4" t="s">
-        <v>179</v>
+      <c r="F76" s="7" t="s">
+        <v>290</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="H76" s="8">
+        <v>286</v>
+      </c>
+      <c r="H76" s="5">
         <v>45731</v>
       </c>
       <c r="I76" s="2">
@@ -5058,41 +5382,48 @@
       <c r="J76" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K76" s="6">
+      <c r="K76" s="5">
         <v>40575</v>
       </c>
-      <c r="L76" s="6">
+      <c r="L76" s="5">
         <v>30161</v>
       </c>
-      <c r="M76" s="6">
+      <c r="M76" s="5">
         <v>50618</v>
       </c>
-      <c r="P76" s="3"/>
-      <c r="S76" s="3"/>
+      <c r="N76" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="O76" s="5">
+        <v>47203</v>
+      </c>
+      <c r="P76" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="77" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A77" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>180</v>
+        <v>292</v>
       </c>
       <c r="C77" s="2">
         <v>55324</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="D77" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F77" s="4" t="s">
-        <v>181</v>
+      <c r="F77" s="7" t="s">
+        <v>293</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="H77" s="8">
+        <v>286</v>
+      </c>
+      <c r="H77" s="5">
         <v>45566</v>
       </c>
       <c r="I77" s="2">
@@ -5101,47 +5432,48 @@
       <c r="J77" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K77" s="6">
+      <c r="K77" s="5">
         <v>40163</v>
       </c>
-      <c r="L77" s="6">
-        <v>32242</v>
-      </c>
-      <c r="M77" s="6">
-        <v>52718</v>
+      <c r="L77" s="5">
+        <v>32390</v>
+      </c>
+      <c r="M77" s="5">
+        <v>52871</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="O77" s="6">
+        <v>294</v>
+      </c>
+      <c r="O77" s="5">
         <v>46744</v>
       </c>
-      <c r="P77" s="3"/>
-      <c r="S77" s="3"/>
+      <c r="P77" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A78" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>182</v>
+        <v>295</v>
       </c>
       <c r="C78" s="2">
         <v>74868</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="D78" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F78" s="4" t="s">
-        <v>183</v>
+      <c r="F78" s="7" t="s">
+        <v>296</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="H78" s="8">
+        <v>286</v>
+      </c>
+      <c r="H78" s="5">
         <v>45839</v>
       </c>
       <c r="I78" s="2">
@@ -5150,47 +5482,48 @@
       <c r="J78" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K78" s="6">
+      <c r="K78" s="5">
         <v>44866</v>
       </c>
-      <c r="L78" s="6">
+      <c r="L78" s="5">
         <v>36799</v>
       </c>
-      <c r="M78" s="6">
+      <c r="M78" s="5">
         <v>57254</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="O78" s="6">
+        <v>297</v>
+      </c>
+      <c r="O78" s="5">
         <v>47324</v>
       </c>
-      <c r="P78" s="3"/>
-      <c r="S78" s="3"/>
+      <c r="P78" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A79" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>184</v>
+        <v>298</v>
       </c>
       <c r="C79" s="2">
         <v>69873</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D79" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F79" s="4" t="s">
-        <v>183</v>
+      <c r="F79" s="7" t="s">
+        <v>296</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="H79" s="8">
+        <v>286</v>
+      </c>
+      <c r="H79" s="5">
         <v>45474</v>
       </c>
       <c r="I79" s="2">
@@ -5199,47 +5532,48 @@
       <c r="J79" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K79" s="6">
+      <c r="K79" s="5">
         <v>42597</v>
       </c>
-      <c r="L79" s="6">
+      <c r="L79" s="5">
         <v>34458</v>
       </c>
-      <c r="M79" s="6">
+      <c r="M79" s="5">
         <v>54940</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="O79" s="6">
+        <v>299</v>
+      </c>
+      <c r="O79" s="5">
         <v>46259</v>
       </c>
-      <c r="P79" s="3"/>
-      <c r="S79" s="3"/>
+      <c r="P79" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A80" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>185</v>
+        <v>300</v>
       </c>
       <c r="C80" s="2">
         <v>59105</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="D80" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F80" s="4" t="s">
-        <v>183</v>
+      <c r="F80" s="7" t="s">
+        <v>296</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="H80" s="6">
+        <v>286</v>
+      </c>
+      <c r="H80" s="5">
         <v>45275</v>
       </c>
       <c r="I80" s="2">
@@ -5248,47 +5582,48 @@
       <c r="J80" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K80" s="6">
-        <v>40545</v>
-      </c>
-      <c r="L80" s="6">
+      <c r="K80" s="5">
+        <v>40575</v>
+      </c>
+      <c r="L80" s="5">
         <v>31215</v>
       </c>
-      <c r="M80" s="6">
+      <c r="M80" s="5">
         <v>51683</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="O80" s="6">
+        <v>301</v>
+      </c>
+      <c r="O80" s="5">
         <v>47005</v>
       </c>
-      <c r="P80" s="3"/>
-      <c r="S80" s="3"/>
+      <c r="P80" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A81" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>186</v>
+        <v>302</v>
       </c>
       <c r="C81" s="2">
         <v>69372</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="D81" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F81" s="4" t="s">
-        <v>187</v>
+      <c r="F81" s="7" t="s">
+        <v>303</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="H81" s="6">
+        <v>286</v>
+      </c>
+      <c r="H81" s="5">
         <v>45170</v>
       </c>
       <c r="I81" s="2">
@@ -5297,47 +5632,48 @@
       <c r="J81" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K81" s="6">
+      <c r="K81" s="5">
         <v>42562</v>
       </c>
-      <c r="L81" s="6">
+      <c r="L81" s="5">
         <v>33749</v>
       </c>
-      <c r="M81" s="6">
+      <c r="M81" s="5">
         <v>54210</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="O81" s="6">
+        <v>304</v>
+      </c>
+      <c r="O81" s="5">
         <v>46259</v>
       </c>
-      <c r="P81" s="3"/>
-      <c r="S81" s="3"/>
+      <c r="P81" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A82" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>188</v>
+        <v>305</v>
       </c>
       <c r="C82" s="2">
         <v>75313</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="D82" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F82" s="4" t="s">
-        <v>187</v>
+      <c r="F82" s="7" t="s">
+        <v>303</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="H82" s="6">
+        <v>286</v>
+      </c>
+      <c r="H82" s="5">
         <v>45536</v>
       </c>
       <c r="I82" s="2">
@@ -5346,47 +5682,48 @@
       <c r="J82" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K82" s="6">
+      <c r="K82" s="5">
         <v>44958</v>
       </c>
-      <c r="L82" s="6">
+      <c r="L82" s="5">
         <v>37757</v>
       </c>
-      <c r="M82" s="6">
+      <c r="M82" s="5">
         <v>58227</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="O82" s="6">
+        <v>306</v>
+      </c>
+      <c r="O82" s="5">
         <v>47114</v>
       </c>
-      <c r="P82" s="3"/>
-      <c r="S82" s="3"/>
+      <c r="P82" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A83" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>189</v>
+        <v>307</v>
       </c>
       <c r="C83" s="2">
         <v>74825</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F83" s="4" t="s">
-        <v>187</v>
+      <c r="F83" s="7" t="s">
+        <v>303</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="H83" s="8">
+        <v>286</v>
+      </c>
+      <c r="H83" s="5">
         <v>45839</v>
       </c>
       <c r="I83" s="2">
@@ -5395,47 +5732,48 @@
       <c r="J83" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K83" s="6">
+      <c r="K83" s="5">
         <v>44866</v>
       </c>
-      <c r="L83" s="6">
+      <c r="L83" s="5">
         <v>37086</v>
       </c>
-      <c r="M83" s="6">
+      <c r="M83" s="5">
         <v>57558</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="O83" s="6">
+        <v>308</v>
+      </c>
+      <c r="O83" s="5">
         <v>47265</v>
       </c>
-      <c r="P83" s="3"/>
-      <c r="S83" s="3"/>
+      <c r="P83" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A84" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>190</v>
+        <v>309</v>
       </c>
       <c r="C84" s="2">
         <v>43249</v>
       </c>
-      <c r="D84" s="3" t="s">
+      <c r="D84" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F84" s="4" t="s">
-        <v>191</v>
+      <c r="F84" s="7" t="s">
+        <v>310</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H84" s="8">
+        <v>311</v>
+      </c>
+      <c r="H84" s="5">
         <v>45458</v>
       </c>
       <c r="I84" s="2">
@@ -5444,41 +5782,57 @@
       <c r="J84" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K84" s="6">
+      <c r="K84" s="5">
         <v>35217</v>
       </c>
-      <c r="L84" s="6">
+      <c r="L84" s="5">
         <v>28017</v>
       </c>
-      <c r="M84" s="6">
+      <c r="M84" s="5">
         <v>48488</v>
       </c>
-      <c r="P84" s="3"/>
-      <c r="S84" s="3"/>
+      <c r="N84" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="O84" s="5">
+        <v>46951</v>
+      </c>
+      <c r="P84" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q84" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="R84" s="5">
+        <v>47232</v>
+      </c>
+      <c r="S84" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="85" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A85" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>193</v>
+        <v>314</v>
       </c>
       <c r="C85" s="2">
         <v>53499</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="D85" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F85" s="4" t="s">
-        <v>194</v>
+      <c r="F85" s="7" t="s">
+        <v>315</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H85" s="8">
+        <v>311</v>
+      </c>
+      <c r="H85" s="5">
         <v>45566</v>
       </c>
       <c r="I85" s="2">
@@ -5487,41 +5841,48 @@
       <c r="J85" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K85" s="6">
+      <c r="K85" s="5">
         <v>39814</v>
       </c>
-      <c r="L85" s="6">
+      <c r="L85" s="5">
         <v>31648</v>
       </c>
-      <c r="M85" s="6">
+      <c r="M85" s="5">
         <v>52110</v>
       </c>
-      <c r="P85" s="3"/>
-      <c r="S85" s="3"/>
+      <c r="N85" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="O85" s="5">
+        <v>47054</v>
+      </c>
+      <c r="P85" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="86" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A86" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>195</v>
+        <v>317</v>
       </c>
       <c r="C86" s="2">
         <v>53234</v>
       </c>
-      <c r="D86" s="3" t="s">
+      <c r="D86" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F86" s="4" t="s">
-        <v>196</v>
+      <c r="F86" s="7" t="s">
+        <v>318</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H86" s="6">
+        <v>311</v>
+      </c>
+      <c r="H86" s="5">
         <v>45597</v>
       </c>
       <c r="I86" s="2">
@@ -5530,47 +5891,48 @@
       <c r="J86" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K86" s="6">
-        <v>39845</v>
-      </c>
-      <c r="L86" s="6">
-        <v>32782</v>
-      </c>
-      <c r="M86" s="6">
-        <v>53267</v>
+      <c r="K86" s="5">
+        <v>39815</v>
+      </c>
+      <c r="L86" s="5">
+        <v>32518</v>
+      </c>
+      <c r="M86" s="5">
+        <v>52994</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="O86" s="6">
+        <v>319</v>
+      </c>
+      <c r="O86" s="5">
         <v>46916</v>
       </c>
-      <c r="P86" s="3"/>
-      <c r="S86" s="3"/>
+      <c r="P86" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A87" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>197</v>
+        <v>320</v>
       </c>
       <c r="C87" s="2">
         <v>48300</v>
       </c>
-      <c r="D87" s="3" t="s">
+      <c r="D87" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F87" s="4" t="s">
-        <v>198</v>
+      <c r="F87" s="7" t="s">
+        <v>321</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H87" s="8">
+        <v>311</v>
+      </c>
+      <c r="H87" s="5">
         <v>45962</v>
       </c>
       <c r="I87" s="2">
@@ -5579,47 +5941,48 @@
       <c r="J87" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K87" s="6">
+      <c r="K87" s="5">
         <v>37135</v>
       </c>
-      <c r="L87" s="6">
+      <c r="L87" s="5">
         <v>28712</v>
       </c>
-      <c r="M87" s="6">
+      <c r="M87" s="5">
         <v>49188</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="O87" s="6">
+        <v>322</v>
+      </c>
+      <c r="O87" s="5">
         <v>47114</v>
       </c>
-      <c r="P87" s="3"/>
-      <c r="S87" s="3"/>
+      <c r="P87" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A88" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>199</v>
+        <v>323</v>
       </c>
       <c r="C88" s="2">
         <v>71340</v>
       </c>
-      <c r="D88" s="3" t="s">
+      <c r="D88" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F88" s="4" t="s">
-        <v>198</v>
+      <c r="F88" s="7" t="s">
+        <v>321</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H88" s="6">
+        <v>311</v>
+      </c>
+      <c r="H88" s="5">
         <v>45474</v>
       </c>
       <c r="I88" s="2">
@@ -5628,47 +5991,48 @@
       <c r="J88" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K88" s="6">
+      <c r="K88" s="5">
         <v>43075</v>
       </c>
-      <c r="L88" s="6">
+      <c r="L88" s="5">
         <v>35418</v>
       </c>
-      <c r="M88" s="6">
+      <c r="M88" s="5">
         <v>55885</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="O88" s="6">
+        <v>324</v>
+      </c>
+      <c r="O88" s="5">
         <v>46574</v>
       </c>
-      <c r="P88" s="3"/>
-      <c r="S88" s="3"/>
+      <c r="P88" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A89" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="C89" s="2">
         <v>75319</v>
       </c>
-      <c r="D89" s="3" t="s">
+      <c r="D89" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F89" s="4" t="s">
-        <v>198</v>
+      <c r="F89" s="7" t="s">
+        <v>321</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H89" s="6">
+        <v>311</v>
+      </c>
+      <c r="H89" s="5">
         <v>45580</v>
       </c>
       <c r="I89" s="2">
@@ -5677,46 +6041,49 @@
       <c r="J89" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K89" s="6">
+      <c r="K89" s="5">
         <v>44958</v>
       </c>
-      <c r="L89" s="6">
+      <c r="L89" s="5">
         <v>35985</v>
       </c>
-      <c r="M89" s="6">
+      <c r="M89" s="5">
         <v>56462</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="O89" s="6">
+        <v>326</v>
+      </c>
+      <c r="O89" s="5">
         <v>47285</v>
+      </c>
+      <c r="P89" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A90" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>201</v>
+        <v>327</v>
       </c>
       <c r="C90" s="2">
         <v>70803</v>
       </c>
-      <c r="D90" s="3" t="s">
+      <c r="D90" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F90" s="4" t="s">
-        <v>202</v>
+      <c r="F90" s="7" t="s">
+        <v>328</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H90" s="6">
-        <v>44927</v>
+        <v>311</v>
+      </c>
+      <c r="H90" s="5">
+        <v>44727</v>
       </c>
       <c r="I90" s="2">
         <v>5</v>
@@ -5724,45 +6091,48 @@
       <c r="J90" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K90" s="6">
+      <c r="K90" s="5">
         <v>42725</v>
       </c>
-      <c r="L90" s="6">
+      <c r="L90" s="5">
         <v>33968</v>
       </c>
-      <c r="M90" s="6">
+      <c r="M90" s="5">
         <v>54424</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="O90" s="6">
+        <v>329</v>
+      </c>
+      <c r="O90" s="5">
         <v>46574</v>
+      </c>
+      <c r="P90" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A91" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>203</v>
+        <v>330</v>
       </c>
       <c r="C91" s="2">
         <v>75323</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D91" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F91" s="4" t="s">
-        <v>202</v>
+      <c r="F91" s="7" t="s">
+        <v>328</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H91" s="6">
+        <v>311</v>
+      </c>
+      <c r="H91" s="5">
         <v>45627</v>
       </c>
       <c r="I91" s="2">
@@ -5771,45 +6141,48 @@
       <c r="J91" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K91" s="6">
+      <c r="K91" s="5">
         <v>44958</v>
       </c>
-      <c r="L91" s="6">
+      <c r="L91" s="5">
         <v>35894</v>
       </c>
-      <c r="M91" s="6">
+      <c r="M91" s="5">
         <v>56370</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="O91" s="6">
+        <v>331</v>
+      </c>
+      <c r="O91" s="5">
         <v>47285</v>
+      </c>
+      <c r="P91" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A92" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>204</v>
+        <v>332</v>
       </c>
       <c r="C92" s="2">
         <v>43219</v>
       </c>
-      <c r="D92" s="3" t="s">
+      <c r="D92" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F92" s="4" t="s">
-        <v>205</v>
+      <c r="F92" s="7" t="s">
+        <v>333</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="H92" s="6">
+        <v>334</v>
+      </c>
+      <c r="H92" s="5">
         <v>45823</v>
       </c>
       <c r="I92" s="2">
@@ -5818,39 +6191,57 @@
       <c r="J92" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K92" s="6">
+      <c r="K92" s="5">
         <v>35217</v>
       </c>
-      <c r="L92" s="6">
+      <c r="L92" s="5">
         <v>27549</v>
       </c>
-      <c r="M92" s="6">
+      <c r="M92" s="5">
         <v>48030</v>
+      </c>
+      <c r="N92" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="O92" s="5">
+        <v>47114</v>
+      </c>
+      <c r="P92" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q92" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="R92" s="5">
+        <v>47370</v>
+      </c>
+      <c r="S92" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="93" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A93" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>207</v>
+        <v>337</v>
       </c>
       <c r="C93" s="2">
         <v>61320</v>
       </c>
-      <c r="D93" s="3" t="s">
+      <c r="D93" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F93" s="4" t="s">
-        <v>208</v>
+      <c r="F93" s="7" t="s">
+        <v>338</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="H93" s="6">
+        <v>334</v>
+      </c>
+      <c r="H93" s="5">
         <v>45823</v>
       </c>
       <c r="I93" s="2">
@@ -5859,39 +6250,48 @@
       <c r="J93" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K93" s="6">
+      <c r="K93" s="5">
         <v>40787</v>
       </c>
-      <c r="L93" s="6">
+      <c r="L93" s="5">
         <v>34085</v>
       </c>
-      <c r="M93" s="6">
+      <c r="M93" s="5">
         <v>54544</v>
+      </c>
+      <c r="N93" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="O93" s="5">
+        <v>46881</v>
+      </c>
+      <c r="P93" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="94" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A94" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>209</v>
+        <v>340</v>
       </c>
       <c r="C94" s="2">
         <v>55449</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D94" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F94" s="4" t="s">
-        <v>210</v>
+      <c r="F94" s="7" t="s">
+        <v>341</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="H94" s="6">
+        <v>334</v>
+      </c>
+      <c r="H94" s="5">
         <v>45566</v>
       </c>
       <c r="I94" s="2">
@@ -5900,45 +6300,48 @@
       <c r="J94" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K94" s="6">
+      <c r="K94" s="5">
         <v>40163</v>
       </c>
-      <c r="L94" s="6">
-        <v>31875</v>
-      </c>
-      <c r="M94" s="6">
+      <c r="L94" s="5">
+        <v>31993</v>
+      </c>
+      <c r="M94" s="5">
         <v>52352</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="O94" s="6">
+        <v>342</v>
+      </c>
+      <c r="O94" s="5">
         <v>47324</v>
+      </c>
+      <c r="P94" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="95" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A95" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>211</v>
+        <v>343</v>
       </c>
       <c r="C95" s="2">
         <v>74668</v>
       </c>
-      <c r="D95" s="3" t="s">
+      <c r="D95" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F95" s="4" t="s">
-        <v>212</v>
+      <c r="F95" s="7" t="s">
+        <v>344</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="H95" s="6">
+        <v>334</v>
+      </c>
+      <c r="H95" s="5">
         <v>45839</v>
       </c>
       <c r="I95" s="2">
@@ -5947,40 +6350,49 @@
       <c r="J95" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K95" s="6">
+      <c r="K95" s="5">
         <v>44866</v>
       </c>
-      <c r="L95" s="6">
+      <c r="L95" s="5">
         <v>37174</v>
       </c>
-      <c r="M95" s="6">
+      <c r="M95" s="5">
         <v>57650</v>
+      </c>
+      <c r="N95" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="O95" s="5">
+        <v>47008</v>
+      </c>
+      <c r="P95" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A96" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>213</v>
+        <v>346</v>
       </c>
       <c r="C96" s="2">
         <v>69567</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="D96" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F96" s="4" t="s">
-        <v>212</v>
+      <c r="F96" s="7" t="s">
+        <v>344</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="H96" s="6">
-        <v>44927</v>
+        <v>334</v>
+      </c>
+      <c r="H96" s="5">
+        <v>44727</v>
       </c>
       <c r="I96" s="2">
         <v>5</v>
@@ -5988,45 +6400,48 @@
       <c r="J96" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K96" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L96" s="6">
+      <c r="K96" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L96" s="5">
         <v>34572</v>
       </c>
-      <c r="M96" s="6">
+      <c r="M96" s="5">
         <v>55032</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="O96" s="6">
+        <v>347</v>
+      </c>
+      <c r="O96" s="5">
         <v>46208</v>
       </c>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P96" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A97" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>214</v>
+        <v>348</v>
       </c>
       <c r="C97" s="2">
         <v>71344</v>
       </c>
-      <c r="D97" s="3" t="s">
+      <c r="D97" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F97" s="4" t="s">
-        <v>215</v>
+      <c r="F97" s="7" t="s">
+        <v>349</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="H97" s="6">
+        <v>334</v>
+      </c>
+      <c r="H97" s="5">
         <v>45627</v>
       </c>
       <c r="I97" s="2">
@@ -6035,45 +6450,48 @@
       <c r="J97" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K97" s="6">
-        <v>42898</v>
-      </c>
-      <c r="L97" s="6">
+      <c r="K97" s="5">
+        <v>43075</v>
+      </c>
+      <c r="L97" s="5">
         <v>34723</v>
       </c>
-      <c r="M97" s="6">
+      <c r="M97" s="5">
         <v>55185</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="O97" s="6">
+        <v>350</v>
+      </c>
+      <c r="O97" s="5">
         <v>46837</v>
       </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P97" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A98" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>216</v>
+        <v>351</v>
       </c>
       <c r="C98" s="2">
         <v>69409</v>
       </c>
-      <c r="D98" s="3" t="s">
+      <c r="D98" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F98" s="4" t="s">
-        <v>215</v>
+      <c r="F98" s="7" t="s">
+        <v>349</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="H98" s="6">
+        <v>334</v>
+      </c>
+      <c r="H98" s="5">
         <v>45474</v>
       </c>
       <c r="I98" s="2">
@@ -6082,45 +6500,48 @@
       <c r="J98" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K98" s="6">
+      <c r="K98" s="5">
         <v>42562</v>
       </c>
-      <c r="L98" s="6">
+      <c r="L98" s="5">
         <v>31920</v>
       </c>
-      <c r="M98" s="6">
+      <c r="M98" s="5">
         <v>52383</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="O98" s="6">
+        <v>352</v>
+      </c>
+      <c r="O98" s="5">
         <v>46305</v>
       </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P98" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A99" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>217</v>
+        <v>353</v>
       </c>
       <c r="C99" s="2">
         <v>64562</v>
       </c>
-      <c r="D99" s="3" t="s">
+      <c r="D99" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F99" s="4" t="s">
-        <v>218</v>
+      <c r="F99" s="7" t="s">
+        <v>354</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H99" s="6">
+        <v>355</v>
+      </c>
+      <c r="H99" s="5">
         <v>45823</v>
       </c>
       <c r="I99" s="2">
@@ -6129,45 +6550,48 @@
       <c r="J99" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K99" s="6">
+      <c r="K99" s="5">
         <v>41791</v>
       </c>
-      <c r="L99" s="6">
-        <v>32813</v>
-      </c>
-      <c r="M99" s="6">
-        <v>53297</v>
+      <c r="L99" s="5">
+        <v>32519</v>
+      </c>
+      <c r="M99" s="5">
+        <v>52994</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="O99" s="6">
+        <v>356</v>
+      </c>
+      <c r="O99" s="5">
         <v>46305</v>
       </c>
-    </row>
-    <row r="100" spans="1:15" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P99" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A100" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>220</v>
+        <v>357</v>
       </c>
       <c r="C100" s="2">
         <v>53497</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="D100" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F100" s="4" t="s">
-        <v>221</v>
+      <c r="F100" s="7" t="s">
+        <v>358</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H100" s="6">
+        <v>355</v>
+      </c>
+      <c r="H100" s="5">
         <v>45566</v>
       </c>
       <c r="I100" s="2">
@@ -6176,45 +6600,48 @@
       <c r="J100" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K100" s="6">
+      <c r="K100" s="5">
         <v>39814</v>
       </c>
-      <c r="L100" s="6">
+      <c r="L100" s="5">
         <v>31350</v>
       </c>
-      <c r="M100" s="6">
+      <c r="M100" s="5">
         <v>51806</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="O100" s="6">
+        <v>359</v>
+      </c>
+      <c r="O100" s="5">
         <v>47414</v>
       </c>
-    </row>
-    <row r="101" spans="1:15" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P100" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A101" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>222</v>
+        <v>360</v>
       </c>
       <c r="C101" s="2">
         <v>55342</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="D101" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F101" s="4" t="s">
-        <v>223</v>
+      <c r="F101" s="7" t="s">
+        <v>361</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H101" s="6">
+        <v>355</v>
+      </c>
+      <c r="H101" s="5">
         <v>45962</v>
       </c>
       <c r="I101" s="2">
@@ -6223,45 +6650,48 @@
       <c r="J101" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K101" s="6">
+      <c r="K101" s="5">
         <v>40163</v>
       </c>
-      <c r="L101" s="6">
+      <c r="L101" s="5">
         <v>33471</v>
       </c>
-      <c r="M101" s="6">
+      <c r="M101" s="5">
         <v>53936</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="O101" s="6">
+        <v>362</v>
+      </c>
+      <c r="O101" s="5">
         <v>47175</v>
       </c>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P101" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A102" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>224</v>
+        <v>363</v>
       </c>
       <c r="C102" s="2">
         <v>61343</v>
       </c>
-      <c r="D102" s="3" t="s">
+      <c r="D102" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F102" s="4" t="s">
-        <v>225</v>
+      <c r="F102" s="7" t="s">
+        <v>364</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H102" s="6">
+        <v>355</v>
+      </c>
+      <c r="H102" s="5">
         <v>45474</v>
       </c>
       <c r="I102" s="2">
@@ -6270,45 +6700,48 @@
       <c r="J102" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K102" s="6">
+      <c r="K102" s="5">
         <v>40787</v>
       </c>
-      <c r="L102" s="6">
+      <c r="L102" s="5">
         <v>34524</v>
       </c>
-      <c r="M102" s="6">
+      <c r="M102" s="5">
         <v>55001</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="O102" s="6">
+        <v>365</v>
+      </c>
+      <c r="O102" s="5">
         <v>47097</v>
       </c>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P102" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A103" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>226</v>
+        <v>366</v>
       </c>
       <c r="C103" s="2">
         <v>74673</v>
       </c>
-      <c r="D103" s="3" t="s">
+      <c r="D103" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F103" s="4" t="s">
-        <v>225</v>
+      <c r="F103" s="7" t="s">
+        <v>364</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H103" s="6">
+        <v>355</v>
+      </c>
+      <c r="H103" s="5">
         <v>45839</v>
       </c>
       <c r="I103" s="2">
@@ -6317,45 +6750,48 @@
       <c r="J103" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K103" s="6">
+      <c r="K103" s="5">
         <v>44866</v>
       </c>
-      <c r="L103" s="6">
+      <c r="L103" s="5">
         <v>37392</v>
       </c>
-      <c r="M103" s="6">
+      <c r="M103" s="5">
         <v>57862</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="O103" s="6">
+        <v>367</v>
+      </c>
+      <c r="O103" s="5">
         <v>47265</v>
       </c>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P103" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A104" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>227</v>
+        <v>368</v>
       </c>
       <c r="C104" s="2">
         <v>70795</v>
       </c>
-      <c r="D104" s="3" t="s">
+      <c r="D104" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F104" s="4" t="s">
-        <v>228</v>
+      <c r="F104" s="7" t="s">
+        <v>369</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H104" s="6">
+        <v>355</v>
+      </c>
+      <c r="H104" s="5">
         <v>45170</v>
       </c>
       <c r="I104" s="2">
@@ -6364,45 +6800,48 @@
       <c r="J104" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K104" s="6">
+      <c r="K104" s="5">
         <v>42725</v>
       </c>
-      <c r="L104" s="6">
+      <c r="L104" s="5">
         <v>34988</v>
       </c>
-      <c r="M104" s="6">
+      <c r="M104" s="5">
         <v>55458</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="O104" s="6">
+        <v>370</v>
+      </c>
+      <c r="O104" s="5">
         <v>46574</v>
       </c>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P104" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A105" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>229</v>
+        <v>371</v>
       </c>
       <c r="C105" s="2">
         <v>70797</v>
       </c>
-      <c r="D105" s="3" t="s">
+      <c r="D105" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F105" s="4" t="s">
-        <v>228</v>
+      <c r="F105" s="7" t="s">
+        <v>369</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H105" s="6">
+        <v>355</v>
+      </c>
+      <c r="H105" s="5">
         <v>45474</v>
       </c>
       <c r="I105" s="2">
@@ -6411,45 +6850,48 @@
       <c r="J105" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K105" s="6">
+      <c r="K105" s="5">
         <v>42725</v>
       </c>
-      <c r="L105" s="6">
+      <c r="L105" s="5">
         <v>35792</v>
       </c>
-      <c r="M105" s="6">
+      <c r="M105" s="5">
         <v>56250</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="O105" s="6">
+        <v>372</v>
+      </c>
+      <c r="O105" s="5">
         <v>46259</v>
       </c>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P105" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A106" s="2" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>230</v>
+        <v>373</v>
       </c>
       <c r="C106" s="2">
         <v>74738</v>
       </c>
-      <c r="D106" s="3" t="s">
+      <c r="D106" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F106" s="4" t="s">
-        <v>228</v>
+      <c r="F106" s="7" t="s">
+        <v>369</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H106" s="6">
+        <v>355</v>
+      </c>
+      <c r="H106" s="5">
         <v>45474</v>
       </c>
       <c r="I106" s="2">
@@ -6458,46 +6900,161 @@
       <c r="J106" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K106" s="6">
+      <c r="K106" s="5">
         <v>44866</v>
       </c>
-      <c r="L106" s="6">
+      <c r="L106" s="5">
         <v>35783</v>
       </c>
-      <c r="M106" s="6">
+      <c r="M106" s="5">
         <v>56250</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="O106" s="6">
+        <v>374</v>
+      </c>
+      <c r="O106" s="5">
         <v>46916</v>
       </c>
-    </row>
+      <c r="P106" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="113" x14ac:dyDescent="0.45"/>
+    <row r="114" x14ac:dyDescent="0.45"/>
+    <row r="115" x14ac:dyDescent="0.45"/>
+    <row r="116" x14ac:dyDescent="0.45"/>
+    <row r="117" x14ac:dyDescent="0.45"/>
+    <row r="118" x14ac:dyDescent="0.45"/>
+    <row r="119" x14ac:dyDescent="0.45"/>
+    <row r="120" x14ac:dyDescent="0.45"/>
+    <row r="121" x14ac:dyDescent="0.45"/>
+    <row r="122" x14ac:dyDescent="0.45"/>
+    <row r="123" x14ac:dyDescent="0.45"/>
+    <row r="124" x14ac:dyDescent="0.45"/>
+    <row r="125" x14ac:dyDescent="0.45"/>
+    <row r="126" x14ac:dyDescent="0.45"/>
+    <row r="127" x14ac:dyDescent="0.45"/>
+    <row r="128" x14ac:dyDescent="0.45"/>
+    <row r="129" x14ac:dyDescent="0.45"/>
+    <row r="130" x14ac:dyDescent="0.45"/>
+    <row r="131" x14ac:dyDescent="0.45"/>
+    <row r="132" x14ac:dyDescent="0.45"/>
+    <row r="133" x14ac:dyDescent="0.45"/>
+    <row r="134" x14ac:dyDescent="0.45"/>
+    <row r="135" x14ac:dyDescent="0.45"/>
+    <row r="136" x14ac:dyDescent="0.45"/>
+    <row r="137" x14ac:dyDescent="0.45"/>
+    <row r="138" x14ac:dyDescent="0.45"/>
+    <row r="139" x14ac:dyDescent="0.45"/>
+    <row r="140" x14ac:dyDescent="0.45"/>
+    <row r="141" x14ac:dyDescent="0.45"/>
+    <row r="142" x14ac:dyDescent="0.45"/>
+    <row r="143" x14ac:dyDescent="0.45"/>
+    <row r="144" x14ac:dyDescent="0.45"/>
+    <row r="145" x14ac:dyDescent="0.45"/>
+    <row r="146" x14ac:dyDescent="0.45"/>
+    <row r="147" x14ac:dyDescent="0.45"/>
+    <row r="148" x14ac:dyDescent="0.45"/>
+    <row r="149" x14ac:dyDescent="0.45"/>
+    <row r="150" x14ac:dyDescent="0.45"/>
+    <row r="151" x14ac:dyDescent="0.45"/>
+    <row r="152" x14ac:dyDescent="0.45"/>
+    <row r="153" x14ac:dyDescent="0.45"/>
+    <row r="154" x14ac:dyDescent="0.45"/>
+    <row r="155" x14ac:dyDescent="0.45"/>
+    <row r="156" x14ac:dyDescent="0.45"/>
+    <row r="157" x14ac:dyDescent="0.45"/>
+    <row r="158" x14ac:dyDescent="0.45"/>
+    <row r="159" x14ac:dyDescent="0.45"/>
+    <row r="160" x14ac:dyDescent="0.45"/>
+    <row r="161" x14ac:dyDescent="0.45"/>
+    <row r="162" x14ac:dyDescent="0.45"/>
+    <row r="163" x14ac:dyDescent="0.45"/>
+    <row r="164" x14ac:dyDescent="0.45"/>
+    <row r="165" x14ac:dyDescent="0.45"/>
+    <row r="166" x14ac:dyDescent="0.45"/>
+    <row r="167" x14ac:dyDescent="0.45"/>
+    <row r="168" x14ac:dyDescent="0.45"/>
+    <row r="169" x14ac:dyDescent="0.45"/>
+    <row r="170" x14ac:dyDescent="0.45"/>
+    <row r="171" x14ac:dyDescent="0.45"/>
+    <row r="172" x14ac:dyDescent="0.45"/>
+    <row r="173" x14ac:dyDescent="0.45"/>
+    <row r="174" x14ac:dyDescent="0.45"/>
+    <row r="175" x14ac:dyDescent="0.45"/>
+    <row r="176" x14ac:dyDescent="0.45"/>
+    <row r="177" x14ac:dyDescent="0.45"/>
+    <row r="178" x14ac:dyDescent="0.45"/>
+    <row r="179" x14ac:dyDescent="0.45"/>
+    <row r="180" x14ac:dyDescent="0.45"/>
+    <row r="181" x14ac:dyDescent="0.45"/>
+    <row r="182" x14ac:dyDescent="0.45"/>
+    <row r="183" x14ac:dyDescent="0.45"/>
+    <row r="184" x14ac:dyDescent="0.45"/>
+    <row r="185" x14ac:dyDescent="0.45"/>
+    <row r="186" x14ac:dyDescent="0.45"/>
+    <row r="187" x14ac:dyDescent="0.45"/>
+    <row r="188" x14ac:dyDescent="0.45"/>
+    <row r="189" x14ac:dyDescent="0.45"/>
+    <row r="190" x14ac:dyDescent="0.45"/>
+    <row r="191" x14ac:dyDescent="0.45"/>
+    <row r="192" x14ac:dyDescent="0.45"/>
+    <row r="193" x14ac:dyDescent="0.45"/>
+    <row r="194" x14ac:dyDescent="0.45"/>
+    <row r="195" x14ac:dyDescent="0.45"/>
+    <row r="196" x14ac:dyDescent="0.45"/>
+    <row r="197" x14ac:dyDescent="0.45"/>
+    <row r="198" x14ac:dyDescent="0.45"/>
+    <row r="199" x14ac:dyDescent="0.45"/>
+    <row r="200" x14ac:dyDescent="0.45"/>
   </sheetData>
-  <autoFilter ref="A1:T144" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:T199" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$A$1:$A$9</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D990</xm:sqref>
+          <xm:sqref>D2:D986</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$B$1:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:J990</xm:sqref>
+          <xm:sqref>J2:J986</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$C$1:$C$15</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I990</xm:sqref>
+          <xm:sqref>I2:I986</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{354EFE19-C43E-4A2D-83B1-FD15C013476E}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$D:$D</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G200</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9DE71029-D453-4F4E-B557-CC5A72AEA9EB}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$E:$E</xm:f>
+          </x14:formula1>
+          <xm:sqref>P2:P200 S2:S200</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{262E53F9-7911-451D-88C9-1E420930ED84}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$F:$F</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E200</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6507,130 +7064,297 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.59765625" customWidth="1"/>
+    <col min="1" max="1" width="16.73046875" style="8" customWidth="1"/>
+    <col min="2" max="3" width="9.06640625" style="8"/>
+    <col min="4" max="4" width="14.46484375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="49.53125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C1">
+      <c r="C1" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+      <c r="D1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+      <c r="D2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="D3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4">
+      <c r="B4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="8">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+      <c r="D4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="8">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
+      <c r="D5" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="8">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
+      <c r="D6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
+      <c r="D7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="8">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+      <c r="D8" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="8">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C10">
+      <c r="D9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C10" s="8">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C11">
+      <c r="D10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C11" s="8">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C12">
+      <c r="D11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C12" s="8">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C13">
+      <c r="D12" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C13" s="8">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C14">
+      <c r="D13" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C14" s="8">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C15">
+      <c r="D14" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C15" s="8">
         <v>18</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="D16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="D17" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F18" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F19" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F20" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F21" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F22" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F23" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F24" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F25" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F26" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
